--- a/gemini/evaluation_results/iou_scores.xlsx
+++ b/gemini/evaluation_results/iou_scores.xlsx
@@ -447,7 +447,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.07883221077835606</v>
+        <v>0.06051764764664517</v>
       </c>
     </row>
     <row r="3">
@@ -477,7 +477,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.1115787945845703</v>
+        <v>0.1038174681367415</v>
       </c>
     </row>
     <row r="6">
@@ -497,7 +497,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.1593094023320456</v>
+        <v>0.1781396107389369</v>
       </c>
     </row>
     <row r="8">
@@ -517,7 +517,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.04061806567663172</v>
+        <v>0.0640237734082757</v>
       </c>
     </row>
     <row r="10">
@@ -527,7 +527,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.07163818394241518</v>
+        <v>0.091825929729472</v>
       </c>
     </row>
     <row r="11">
@@ -537,7 +537,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.0857184216721265</v>
+        <v>0.0740592933793416</v>
       </c>
     </row>
     <row r="12">
@@ -585,7 +585,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.02330434648724473</v>
+        <v>0.05596733647051951</v>
       </c>
     </row>
     <row r="17">
@@ -655,7 +655,7 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.0154711349107916</v>
+        <v>0.01513687076302941</v>
       </c>
     </row>
     <row r="24">
@@ -665,7 +665,7 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.1654963210205174</v>
+        <v>0.2360090038329747</v>
       </c>
     </row>
     <row r="25">
@@ -675,7 +675,7 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.1433505928171762</v>
+        <v>0.1616360026038227</v>
       </c>
     </row>
     <row r="26">
@@ -685,7 +685,7 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.1242506443294255</v>
+        <v>0.08189362107800345</v>
       </c>
     </row>
     <row r="27">
@@ -695,7 +695,7 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.1691077032471785</v>
+        <v>0.1569078967806601</v>
       </c>
     </row>
     <row r="28">
@@ -705,7 +705,7 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.0280084022966823</v>
+        <v>0.02915684764768806</v>
       </c>
     </row>
     <row r="29">
@@ -725,7 +725,7 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0.09908832673830457</v>
+        <v>0.09201058911413997</v>
       </c>
     </row>
     <row r="31">
@@ -753,7 +753,7 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>0.1542501261323398</v>
+        <v>0.1257645656456247</v>
       </c>
     </row>
     <row r="34">
@@ -773,7 +773,7 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>0.1649010723177386</v>
+        <v>0.2221969898592428</v>
       </c>
     </row>
     <row r="36">
@@ -783,7 +783,7 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>0.08876407542796269</v>
+        <v>0.08382432997509907</v>
       </c>
     </row>
     <row r="37">
@@ -813,7 +813,7 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>0.1106811395893688</v>
+        <v>0.0872329559945496</v>
       </c>
     </row>
     <row r="40">
@@ -823,7 +823,7 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>0.03802861661577499</v>
+        <v>0.04188433728689261</v>
       </c>
     </row>
     <row r="41">
@@ -833,7 +833,7 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>0.1296384073152812</v>
+        <v>0.1413718076563293</v>
       </c>
     </row>
     <row r="42">
@@ -861,7 +861,7 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>0.1920742498638831</v>
+        <v>0.2185978781903138</v>
       </c>
     </row>
     <row r="45">
@@ -891,7 +891,7 @@
         </is>
       </c>
       <c r="B47" t="n">
-        <v>0.01687843337201982</v>
+        <v>0.05020861662669689</v>
       </c>
     </row>
     <row r="48">
@@ -931,7 +931,7 @@
         </is>
       </c>
       <c r="B51" t="n">
-        <v>0.1226386979675044</v>
+        <v>0.1032694836097124</v>
       </c>
     </row>
     <row r="52">
@@ -967,7 +967,7 @@
         </is>
       </c>
       <c r="B55" t="n">
-        <v>0.09783034042982873</v>
+        <v>0.09925477522439713</v>
       </c>
     </row>
     <row r="56">
@@ -977,7 +977,7 @@
         </is>
       </c>
       <c r="B56" t="n">
-        <v>0.004511097364917315</v>
+        <v>0.04009178037816191</v>
       </c>
     </row>
     <row r="57">
@@ -987,7 +987,7 @@
         </is>
       </c>
       <c r="B57" t="n">
-        <v>0.1143910009620401</v>
+        <v>0.1317626132751147</v>
       </c>
     </row>
     <row r="58">
@@ -1007,7 +1007,7 @@
         </is>
       </c>
       <c r="B59" t="n">
-        <v>0.02992523376206526</v>
+        <v>0.03813744334555278</v>
       </c>
     </row>
     <row r="60">
@@ -1017,7 +1017,7 @@
         </is>
       </c>
       <c r="B60" t="n">
-        <v>0.0584174380129931</v>
+        <v>0.0862557070616468</v>
       </c>
     </row>
     <row r="61">
@@ -1027,7 +1027,7 @@
         </is>
       </c>
       <c r="B61" t="n">
-        <v>0.1297599765051399</v>
+        <v>0.1473103804324892</v>
       </c>
     </row>
     <row r="62">
@@ -1037,7 +1037,7 @@
         </is>
       </c>
       <c r="B62" t="n">
-        <v>0.01081905728522901</v>
+        <v>0.01573472086818887</v>
       </c>
     </row>
     <row r="63">
@@ -1047,7 +1047,7 @@
         </is>
       </c>
       <c r="B63" t="n">
-        <v>0.1067854832732066</v>
+        <v>0.1259669834081098</v>
       </c>
     </row>
     <row r="64">
@@ -1067,7 +1067,7 @@
         </is>
       </c>
       <c r="B65" t="n">
-        <v>0.1840464733854204</v>
+        <v>0.1689714606887595</v>
       </c>
     </row>
     <row r="66">
@@ -1087,7 +1087,7 @@
         </is>
       </c>
       <c r="B67" t="n">
-        <v>0.04155358317772548</v>
+        <v>0.05291714374097532</v>
       </c>
     </row>
     <row r="68">
@@ -1107,7 +1107,7 @@
         </is>
       </c>
       <c r="B69" t="n">
-        <v>0.07175606376169866</v>
+        <v>0.06966140087854034</v>
       </c>
     </row>
     <row r="70">
@@ -1117,7 +1117,7 @@
         </is>
       </c>
       <c r="B70" t="n">
-        <v>0.08118865051390699</v>
+        <v>0.07923277295224335</v>
       </c>
     </row>
     <row r="71">
@@ -1127,7 +1127,7 @@
         </is>
       </c>
       <c r="B71" t="n">
-        <v>0.03217203216237132</v>
+        <v>0.02443272349811004</v>
       </c>
     </row>
     <row r="72">
@@ -1147,7 +1147,7 @@
         </is>
       </c>
       <c r="B73" t="n">
-        <v>0.08175827995534578</v>
+        <v>0.08085722513410486</v>
       </c>
     </row>
     <row r="74">
@@ -1157,7 +1157,7 @@
         </is>
       </c>
       <c r="B74" t="n">
-        <v>0.09321748941664965</v>
+        <v>0.08645526899340381</v>
       </c>
     </row>
     <row r="75">
@@ -1187,7 +1187,7 @@
         </is>
       </c>
       <c r="B77" t="n">
-        <v>0.124032383087406</v>
+        <v>0.1198979703178258</v>
       </c>
     </row>
     <row r="78">
@@ -1197,7 +1197,7 @@
         </is>
       </c>
       <c r="B78" t="n">
-        <v>0.08883560531864913</v>
+        <v>0.09517047362818983</v>
       </c>
     </row>
     <row r="79">
@@ -1207,7 +1207,7 @@
         </is>
       </c>
       <c r="B79" t="n">
-        <v>0.127823839615365</v>
+        <v>0.1396396529351549</v>
       </c>
     </row>
     <row r="80">
@@ -1217,7 +1217,7 @@
         </is>
       </c>
       <c r="B80" t="n">
-        <v>0.1535786773073195</v>
+        <v>0.130826280669198</v>
       </c>
     </row>
     <row r="81">
@@ -1227,7 +1227,7 @@
         </is>
       </c>
       <c r="B81" t="n">
-        <v>0.02321465457735216</v>
+        <v>0.02359801769967381</v>
       </c>
     </row>
     <row r="82">
@@ -1237,7 +1237,7 @@
         </is>
       </c>
       <c r="B82" t="n">
-        <v>0.08139008220741877</v>
+        <v>0.1203965677755821</v>
       </c>
     </row>
     <row r="83">
@@ -1247,7 +1247,7 @@
         </is>
       </c>
       <c r="B83" t="n">
-        <v>0.07378833588101695</v>
+        <v>0.06708030534637904</v>
       </c>
     </row>
     <row r="84">
@@ -1257,7 +1257,7 @@
         </is>
       </c>
       <c r="B84" t="n">
-        <v>0.09130314158078134</v>
+        <v>0.03543941077999858</v>
       </c>
     </row>
     <row r="85">
@@ -1277,7 +1277,7 @@
         </is>
       </c>
       <c r="B86" t="n">
-        <v>0.02557799888437587</v>
+        <v>0.02292368745330779</v>
       </c>
     </row>
     <row r="87">
@@ -1287,7 +1287,7 @@
         </is>
       </c>
       <c r="B87" t="n">
-        <v>0.04844225964938064</v>
+        <v>0.05559804002399343</v>
       </c>
     </row>
     <row r="88">
@@ -1297,7 +1297,7 @@
         </is>
       </c>
       <c r="B88" t="n">
-        <v>0.0562349643078163</v>
+        <v>0.03576159207981704</v>
       </c>
     </row>
     <row r="89">
@@ -1307,7 +1307,7 @@
         </is>
       </c>
       <c r="B89" t="n">
-        <v>0.1174457092555235</v>
+        <v>0.1024279807870987</v>
       </c>
     </row>
     <row r="90">
@@ -1317,7 +1317,7 @@
         </is>
       </c>
       <c r="B90" t="n">
-        <v>0.07506456991587816</v>
+        <v>0.1178043064803409</v>
       </c>
     </row>
     <row r="91">
@@ -1375,7 +1375,7 @@
         </is>
       </c>
       <c r="B96" t="n">
-        <v>0.2116030510106292</v>
+        <v>0.2111814999926092</v>
       </c>
     </row>
     <row r="97">
@@ -1385,7 +1385,7 @@
         </is>
       </c>
       <c r="B97" t="n">
-        <v>0.1465302216348721</v>
+        <v>0.07014165418390471</v>
       </c>
     </row>
     <row r="98">
@@ -1395,7 +1395,7 @@
         </is>
       </c>
       <c r="B98" t="n">
-        <v>0.01999277870955743</v>
+        <v>0.0182287099998906</v>
       </c>
     </row>
     <row r="99">
@@ -1455,7 +1455,7 @@
         </is>
       </c>
       <c r="B104" t="n">
-        <v>0.1041876123211378</v>
+        <v>0.05298916120479725</v>
       </c>
     </row>
     <row r="105">
@@ -1475,7 +1475,7 @@
         </is>
       </c>
       <c r="B106" t="n">
-        <v>0.02969209616002884</v>
+        <v>0.07141852018381568</v>
       </c>
     </row>
     <row r="107">
@@ -1485,7 +1485,7 @@
         </is>
       </c>
       <c r="B107" t="n">
-        <v>0.1379982572942049</v>
+        <v>0.1329349974062483</v>
       </c>
     </row>
     <row r="108">
@@ -1535,7 +1535,7 @@
         </is>
       </c>
       <c r="B112" t="n">
-        <v>0.04178913312370016</v>
+        <v>0.06274084204318291</v>
       </c>
     </row>
     <row r="113">
@@ -1545,7 +1545,7 @@
         </is>
       </c>
       <c r="B113" t="n">
-        <v>0.06894395420483286</v>
+        <v>0.07987908517291167</v>
       </c>
     </row>
     <row r="114">
@@ -1555,7 +1555,7 @@
         </is>
       </c>
       <c r="B114" t="n">
-        <v>0.06762674322679267</v>
+        <v>0.08572448353417721</v>
       </c>
     </row>
     <row r="115">
@@ -1595,7 +1595,7 @@
         </is>
       </c>
       <c r="B118" t="n">
-        <v>0.03089168626115122</v>
+        <v>0.06199242581056374</v>
       </c>
     </row>
     <row r="119">
@@ -1625,7 +1625,7 @@
         </is>
       </c>
       <c r="B121" t="n">
-        <v>0.08211143490191848</v>
+        <v>0.08241132314386299</v>
       </c>
     </row>
     <row r="122">
@@ -1635,7 +1635,7 @@
         </is>
       </c>
       <c r="B122" t="n">
-        <v>0.09983944342805615</v>
+        <v>0</v>
       </c>
     </row>
     <row r="123">
@@ -1645,7 +1645,7 @@
         </is>
       </c>
       <c r="B123" t="n">
-        <v>0.03134573616390812</v>
+        <v>0.02893452568976133</v>
       </c>
     </row>
     <row r="124">
@@ -1673,7 +1673,7 @@
         </is>
       </c>
       <c r="B126" t="n">
-        <v>0.0009021166111162119</v>
+        <v>0.01652967441715559</v>
       </c>
     </row>
     <row r="127">
@@ -1683,7 +1683,7 @@
         </is>
       </c>
       <c r="B127" t="n">
-        <v>0.09997367225077296</v>
+        <v>0.0572366446899022</v>
       </c>
     </row>
     <row r="128">
@@ -1693,7 +1693,7 @@
         </is>
       </c>
       <c r="B128" t="n">
-        <v>0.0747158743816978</v>
+        <v>0.08580871455022897</v>
       </c>
     </row>
     <row r="129">
@@ -1713,7 +1713,7 @@
         </is>
       </c>
       <c r="B130" t="n">
-        <v>0.08144551594134504</v>
+        <v>0.07206080287405678</v>
       </c>
     </row>
     <row r="131">
@@ -1723,7 +1723,7 @@
         </is>
       </c>
       <c r="B131" t="n">
-        <v>0.1741633774669946</v>
+        <v>0.1832699622071891</v>
       </c>
     </row>
     <row r="132">
@@ -1733,7 +1733,7 @@
         </is>
       </c>
       <c r="B132" t="n">
-        <v>0.09974310038642335</v>
+        <v>0.11932952415937</v>
       </c>
     </row>
     <row r="133">
@@ -1753,7 +1753,7 @@
         </is>
       </c>
       <c r="B134" t="n">
-        <v>0.09131382184721605</v>
+        <v>0.08522623372406832</v>
       </c>
     </row>
     <row r="135">
@@ -1763,7 +1763,7 @@
         </is>
       </c>
       <c r="B135" t="n">
-        <v>0.065962304490183</v>
+        <v>0.05814268362137383</v>
       </c>
     </row>
     <row r="136">
@@ -1773,7 +1773,7 @@
         </is>
       </c>
       <c r="B136" t="n">
-        <v>0.1636778884718355</v>
+        <v>0.1559354870932186</v>
       </c>
     </row>
     <row r="137">
@@ -1783,7 +1783,7 @@
         </is>
       </c>
       <c r="B137" t="n">
-        <v>0.04262677994032082</v>
+        <v>0.04794700900028918</v>
       </c>
     </row>
     <row r="138">
@@ -1793,7 +1793,7 @@
         </is>
       </c>
       <c r="B138" t="n">
-        <v>0.01983584362001824</v>
+        <v>0.0495985938613151</v>
       </c>
     </row>
     <row r="139">
@@ -1803,7 +1803,7 @@
         </is>
       </c>
       <c r="B139" t="n">
-        <v>0.1121559669122934</v>
+        <v>0.1566085320928998</v>
       </c>
     </row>
     <row r="140">
@@ -1813,7 +1813,7 @@
         </is>
       </c>
       <c r="B140" t="n">
-        <v>0.006424366854453613</v>
+        <v>0.08278529378006685</v>
       </c>
     </row>
     <row r="141">
@@ -1823,7 +1823,7 @@
         </is>
       </c>
       <c r="B141" t="n">
-        <v>0.05401416355453331</v>
+        <v>0.04956310539500655</v>
       </c>
     </row>
     <row r="142">
@@ -1863,7 +1863,7 @@
         </is>
       </c>
       <c r="B145" t="n">
-        <v>0.07840680940428814</v>
+        <v>0.06160535024622639</v>
       </c>
     </row>
     <row r="146">
@@ -1873,7 +1873,7 @@
         </is>
       </c>
       <c r="B146" t="n">
-        <v>0.07446129225382891</v>
+        <v>0.05908640394889603</v>
       </c>
     </row>
     <row r="147">
@@ -1883,7 +1883,7 @@
         </is>
       </c>
       <c r="B147" t="n">
-        <v>0.06351054193787925</v>
+        <v>0.05936855007236539</v>
       </c>
     </row>
     <row r="148">
@@ -1893,7 +1893,7 @@
         </is>
       </c>
       <c r="B148" t="n">
-        <v>0.05616358174567182</v>
+        <v>0.07738546162733612</v>
       </c>
     </row>
     <row r="149">
@@ -1911,7 +1911,7 @@
         </is>
       </c>
       <c r="B150" t="n">
-        <v>0.05483661278024768</v>
+        <v>0.02613960191751631</v>
       </c>
     </row>
     <row r="151">
@@ -1921,7 +1921,7 @@
         </is>
       </c>
       <c r="B151" t="n">
-        <v>0.09706040781827271</v>
+        <v>0.1049429548582314</v>
       </c>
     </row>
     <row r="152">
@@ -1971,7 +1971,7 @@
         </is>
       </c>
       <c r="B156" t="n">
-        <v>0.1214751217724626</v>
+        <v>0.109221462994345</v>
       </c>
     </row>
     <row r="157">
@@ -1991,7 +1991,7 @@
         </is>
       </c>
       <c r="B158" t="n">
-        <v>0.08664168038554546</v>
+        <v>0.1031022975748596</v>
       </c>
     </row>
     <row r="159">
@@ -2011,7 +2011,7 @@
         </is>
       </c>
       <c r="B160" t="n">
-        <v>0.1412637480131897</v>
+        <v>0.1381730997553259</v>
       </c>
     </row>
     <row r="161">
@@ -2079,7 +2079,7 @@
         </is>
       </c>
       <c r="B167" t="n">
-        <v>0.0159405787854747</v>
+        <v>0.01541793685808208</v>
       </c>
     </row>
     <row r="168">
@@ -2089,7 +2089,7 @@
         </is>
       </c>
       <c r="B168" t="n">
-        <v>0.1156547170123309</v>
+        <v>0.1103814477936036</v>
       </c>
     </row>
     <row r="169">
@@ -2109,7 +2109,7 @@
         </is>
       </c>
       <c r="B170" t="n">
-        <v>0.03461720850004719</v>
+        <v>0.01833353996514341</v>
       </c>
     </row>
     <row r="171">
@@ -2119,7 +2119,7 @@
         </is>
       </c>
       <c r="B171" t="n">
-        <v>0.02643658690145982</v>
+        <v>0.02056178981224652</v>
       </c>
     </row>
     <row r="172">
@@ -2129,7 +2129,7 @@
         </is>
       </c>
       <c r="B172" t="n">
-        <v>0.1601909088240762</v>
+        <v>0.1705674588846694</v>
       </c>
     </row>
     <row r="173">
@@ -2139,7 +2139,7 @@
         </is>
       </c>
       <c r="B173" t="n">
-        <v>0.2292221865195291</v>
+        <v>0.2341276139546641</v>
       </c>
     </row>
     <row r="174">
@@ -2169,7 +2169,7 @@
         </is>
       </c>
       <c r="B176" t="n">
-        <v>0.09129662832849803</v>
+        <v>0.06514136401689244</v>
       </c>
     </row>
     <row r="177">
@@ -2189,7 +2189,7 @@
         </is>
       </c>
       <c r="B178" t="n">
-        <v>0.1161411886210434</v>
+        <v>0.123264186557811</v>
       </c>
     </row>
     <row r="179">
@@ -2219,7 +2219,7 @@
         </is>
       </c>
       <c r="B181" t="n">
-        <v>0.09794332290602872</v>
+        <v>0.1348783448401431</v>
       </c>
     </row>
     <row r="182">
@@ -2287,7 +2287,7 @@
         </is>
       </c>
       <c r="B188" t="n">
-        <v>0.2985896792991435</v>
+        <v>0.3086284630288238</v>
       </c>
     </row>
     <row r="189">
@@ -2307,7 +2307,7 @@
         </is>
       </c>
       <c r="B190" t="n">
-        <v>0.04692302957888351</v>
+        <v>0.04646370155666172</v>
       </c>
     </row>
     <row r="191">
@@ -2327,7 +2327,7 @@
         </is>
       </c>
       <c r="B192" t="n">
-        <v>0.05200405817994383</v>
+        <v>0.05074053507888362</v>
       </c>
     </row>
     <row r="193">
@@ -2337,7 +2337,7 @@
         </is>
       </c>
       <c r="B193" t="n">
-        <v>0.2193044196650311</v>
+        <v>0.2492485294690917</v>
       </c>
     </row>
     <row r="194">
@@ -2347,7 +2347,7 @@
         </is>
       </c>
       <c r="B194" t="n">
-        <v>0.03711411922377227</v>
+        <v>0.02295852653714258</v>
       </c>
     </row>
     <row r="195">
@@ -2357,7 +2357,7 @@
         </is>
       </c>
       <c r="B195" t="n">
-        <v>0.04110928578508541</v>
+        <v>0.0346626611853188</v>
       </c>
     </row>
     <row r="196">
@@ -2377,7 +2377,7 @@
         </is>
       </c>
       <c r="B197" t="n">
-        <v>0.07462721761173771</v>
+        <v>0.09225130449807213</v>
       </c>
     </row>
     <row r="198">
@@ -2407,7 +2407,7 @@
         </is>
       </c>
       <c r="B200" t="n">
-        <v>0.1972859757644319</v>
+        <v>0.1069328960685775</v>
       </c>
     </row>
     <row r="201">
@@ -2417,7 +2417,7 @@
         </is>
       </c>
       <c r="B201" t="n">
-        <v>0.07390030303104593</v>
+        <v>0.08410881932206371</v>
       </c>
     </row>
     <row r="202">
@@ -2427,7 +2427,7 @@
         </is>
       </c>
       <c r="B202" t="n">
-        <v>0.03593127479473311</v>
+        <v>0.04585764788080155</v>
       </c>
     </row>
     <row r="203">
@@ -2447,7 +2447,7 @@
         </is>
       </c>
       <c r="B204" t="n">
-        <v>0.04628958697721906</v>
+        <v>0.04759281457638095</v>
       </c>
     </row>
     <row r="205">
@@ -2457,7 +2457,7 @@
         </is>
       </c>
       <c r="B205" t="n">
-        <v>0.02188785062788853</v>
+        <v>0.03839286229174682</v>
       </c>
     </row>
     <row r="206">
@@ -2467,7 +2467,7 @@
         </is>
       </c>
       <c r="B206" t="n">
-        <v>0.003853358891696437</v>
+        <v>0.008159910898346582</v>
       </c>
     </row>
     <row r="207">
@@ -2477,7 +2477,7 @@
         </is>
       </c>
       <c r="B207" t="n">
-        <v>0.07863577839283023</v>
+        <v>0.07945166213868281</v>
       </c>
     </row>
     <row r="208">
@@ -2487,7 +2487,7 @@
         </is>
       </c>
       <c r="B208" t="n">
-        <v>0.03619308834938292</v>
+        <v>0.02767706756129282</v>
       </c>
     </row>
     <row r="209">
@@ -2507,7 +2507,7 @@
         </is>
       </c>
       <c r="B210" t="n">
-        <v>0.0831832534861235</v>
+        <v>0.09127896327334821</v>
       </c>
     </row>
     <row r="211">
@@ -2517,7 +2517,7 @@
         </is>
       </c>
       <c r="B211" t="n">
-        <v>0.03803568465277974</v>
+        <v>0.03548482022974128</v>
       </c>
     </row>
     <row r="212">
@@ -2527,7 +2527,7 @@
         </is>
       </c>
       <c r="B212" t="n">
-        <v>0.1743528325043967</v>
+        <v>0.1721322832967015</v>
       </c>
     </row>
     <row r="213">
@@ -2537,7 +2537,7 @@
         </is>
       </c>
       <c r="B213" t="n">
-        <v>0.00997727357301533</v>
+        <v>0.01887171877545971</v>
       </c>
     </row>
     <row r="214">
@@ -2557,7 +2557,7 @@
         </is>
       </c>
       <c r="B215" t="n">
-        <v>0.04917628860652187</v>
+        <v>0.06364130558050972</v>
       </c>
     </row>
     <row r="216">
@@ -2567,7 +2567,7 @@
         </is>
       </c>
       <c r="B216" t="n">
-        <v>0.1216828183337652</v>
+        <v>0.1141926245074901</v>
       </c>
     </row>
     <row r="217">
@@ -2587,7 +2587,7 @@
         </is>
       </c>
       <c r="B218" t="n">
-        <v>0.116874324243698</v>
+        <v>0.1141001481126966</v>
       </c>
     </row>
     <row r="219">
@@ -2597,7 +2597,7 @@
         </is>
       </c>
       <c r="B219" t="n">
-        <v>0.1511008505800125</v>
+        <v>0.1508671687645879</v>
       </c>
     </row>
     <row r="220">
@@ -2607,7 +2607,7 @@
         </is>
       </c>
       <c r="B220" t="n">
-        <v>0.07146949035104037</v>
+        <v>0.05962516560183738</v>
       </c>
     </row>
     <row r="221">
@@ -2617,7 +2617,7 @@
         </is>
       </c>
       <c r="B221" t="n">
-        <v>0.093117938846442</v>
+        <v>0.1450167102555082</v>
       </c>
     </row>
     <row r="222">
@@ -2637,7 +2637,7 @@
         </is>
       </c>
       <c r="B223" t="n">
-        <v>0.103026393851249</v>
+        <v>0.1076236378700315</v>
       </c>
     </row>
     <row r="224">
@@ -2647,7 +2647,7 @@
         </is>
       </c>
       <c r="B224" t="n">
-        <v>0.08015665732082763</v>
+        <v>0.0452169999980076</v>
       </c>
     </row>
     <row r="225">
@@ -2657,7 +2657,7 @@
         </is>
       </c>
       <c r="B225" t="n">
-        <v>0.04206282346634331</v>
+        <v>0.04087897631776809</v>
       </c>
     </row>
     <row r="226">
@@ -2667,7 +2667,7 @@
         </is>
       </c>
       <c r="B226" t="n">
-        <v>0.0698331207176493</v>
+        <v>0.08180145140296793</v>
       </c>
     </row>
     <row r="227">
@@ -2687,7 +2687,7 @@
         </is>
       </c>
       <c r="B228" t="n">
-        <v>0.01527975759192448</v>
+        <v>0.03067412503764302</v>
       </c>
     </row>
     <row r="229">
@@ -2717,7 +2717,7 @@
         </is>
       </c>
       <c r="B231" t="n">
-        <v>0.04312780530946451</v>
+        <v>0.07251189160085911</v>
       </c>
     </row>
     <row r="232">
@@ -2727,7 +2727,7 @@
         </is>
       </c>
       <c r="B232" t="n">
-        <v>0.1530602139848202</v>
+        <v>0.1620903430782231</v>
       </c>
     </row>
     <row r="233">
@@ -2767,7 +2767,7 @@
         </is>
       </c>
       <c r="B236" t="n">
-        <v>0.04847517995010476</v>
+        <v>0.04059218260013678</v>
       </c>
     </row>
     <row r="237">
@@ -2777,7 +2777,7 @@
         </is>
       </c>
       <c r="B237" t="n">
-        <v>0.01860078590398436</v>
+        <v>0.02082712967373208</v>
       </c>
     </row>
     <row r="238">
@@ -2787,7 +2787,7 @@
         </is>
       </c>
       <c r="B238" t="n">
-        <v>0.07611323462866014</v>
+        <v>0.05718636260608315</v>
       </c>
     </row>
     <row r="239">
@@ -2797,7 +2797,7 @@
         </is>
       </c>
       <c r="B239" t="n">
-        <v>0.05787333407499749</v>
+        <v>0.06067571077053117</v>
       </c>
     </row>
     <row r="240">
@@ -2807,7 +2807,7 @@
         </is>
       </c>
       <c r="B240" t="n">
-        <v>0.1213108770227359</v>
+        <v>0.1323586653078712</v>
       </c>
     </row>
     <row r="241">
@@ -2817,7 +2817,7 @@
         </is>
       </c>
       <c r="B241" t="n">
-        <v>0.01633611737441545</v>
+        <v>0.02511515924379994</v>
       </c>
     </row>
     <row r="242">
@@ -2837,7 +2837,7 @@
         </is>
       </c>
       <c r="B243" t="n">
-        <v>0.01554016568137544</v>
+        <v>0.01491855905412042</v>
       </c>
     </row>
     <row r="244">
@@ -2857,7 +2857,7 @@
         </is>
       </c>
       <c r="B245" t="n">
-        <v>0.09139431916780145</v>
+        <v>0.1055605854125545</v>
       </c>
     </row>
     <row r="246">
@@ -2867,7 +2867,7 @@
         </is>
       </c>
       <c r="B246" t="n">
-        <v>0.05989642605751022</v>
+        <v>0.07396031269071095</v>
       </c>
     </row>
     <row r="247">
@@ -2887,7 +2887,7 @@
         </is>
       </c>
       <c r="B248" t="n">
-        <v>0.04772997979815426</v>
+        <v>0.04818598564312843</v>
       </c>
     </row>
     <row r="249">
@@ -2897,7 +2897,7 @@
         </is>
       </c>
       <c r="B249" t="n">
-        <v>0.01937915704460527</v>
+        <v>0.01661070603823309</v>
       </c>
     </row>
     <row r="250">
@@ -2907,7 +2907,7 @@
         </is>
       </c>
       <c r="B250" t="n">
-        <v>0.1790557057699009</v>
+        <v>0.1707275334085102</v>
       </c>
     </row>
     <row r="251">
@@ -2917,7 +2917,7 @@
         </is>
       </c>
       <c r="B251" t="n">
-        <v>0.0173010845651244</v>
+        <v>0.02734739503234051</v>
       </c>
     </row>
     <row r="252">
@@ -2927,7 +2927,7 @@
         </is>
       </c>
       <c r="B252" t="n">
-        <v>0.1964307453638091</v>
+        <v>0.2299423601663837</v>
       </c>
     </row>
     <row r="253">
@@ -2957,7 +2957,7 @@
         </is>
       </c>
       <c r="B255" t="n">
-        <v>0.05385131645273501</v>
+        <v>0.05880378324293799</v>
       </c>
     </row>
     <row r="256">
@@ -2977,7 +2977,7 @@
         </is>
       </c>
       <c r="B257" t="n">
-        <v>0.2207353084383505</v>
+        <v>0.2177013760599194</v>
       </c>
     </row>
     <row r="258">
@@ -2987,7 +2987,7 @@
         </is>
       </c>
       <c r="B258" t="n">
-        <v>0.08991711981541589</v>
+        <v>0.05994474654361059</v>
       </c>
     </row>
     <row r="259">
@@ -3007,7 +3007,7 @@
         </is>
       </c>
       <c r="B260" t="n">
-        <v>0.08406896950142018</v>
+        <v>0.09666202023709809</v>
       </c>
     </row>
     <row r="261">
@@ -3027,7 +3027,7 @@
         </is>
       </c>
       <c r="B262" t="n">
-        <v>0.2317158347810879</v>
+        <v>0.2148907099555648</v>
       </c>
     </row>
     <row r="263">
@@ -3045,7 +3045,7 @@
         </is>
       </c>
       <c r="B264" t="n">
-        <v>0.112763795767601</v>
+        <v>0.03936924861198607</v>
       </c>
     </row>
     <row r="265">
@@ -3055,7 +3055,7 @@
         </is>
       </c>
       <c r="B265" t="n">
-        <v>0.01437603053982364</v>
+        <v>0.02011293864425934</v>
       </c>
     </row>
     <row r="266">
@@ -3083,7 +3083,7 @@
         </is>
       </c>
       <c r="B268" t="n">
-        <v>0.04701132929532396</v>
+        <v>0.0475213228236847</v>
       </c>
     </row>
     <row r="269">
@@ -3123,7 +3123,7 @@
         </is>
       </c>
       <c r="B272" t="n">
-        <v>0.02497406754722311</v>
+        <v>0.05419028945675704</v>
       </c>
     </row>
     <row r="273">
@@ -3133,7 +3133,7 @@
         </is>
       </c>
       <c r="B273" t="n">
-        <v>0.04103482029675903</v>
+        <v>0.03418755029264493</v>
       </c>
     </row>
     <row r="274">
@@ -3153,7 +3153,7 @@
         </is>
       </c>
       <c r="B275" t="n">
-        <v>0.1873650994724982</v>
+        <v>0.1972870837916141</v>
       </c>
     </row>
     <row r="276">
@@ -3163,7 +3163,7 @@
         </is>
       </c>
       <c r="B276" t="n">
-        <v>0.04209856827192898</v>
+        <v>0.0447450702431005</v>
       </c>
     </row>
     <row r="277">
@@ -3173,7 +3173,7 @@
         </is>
       </c>
       <c r="B277" t="n">
-        <v>0.1750567803793957</v>
+        <v>0.1469469991462353</v>
       </c>
     </row>
     <row r="278">
@@ -3193,7 +3193,7 @@
         </is>
       </c>
       <c r="B279" t="n">
-        <v>0.1496121934024591</v>
+        <v>0.151163777605671</v>
       </c>
     </row>
     <row r="280">
@@ -3203,7 +3203,7 @@
         </is>
       </c>
       <c r="B280" t="n">
-        <v>0.1121365604108114</v>
+        <v>0.1104439839878246</v>
       </c>
     </row>
     <row r="281">
@@ -3283,7 +3283,7 @@
         </is>
       </c>
       <c r="B288" t="n">
-        <v>0.2589925681914947</v>
+        <v>0.1755240629253653</v>
       </c>
     </row>
     <row r="289">
@@ -3293,7 +3293,7 @@
         </is>
       </c>
       <c r="B289" t="n">
-        <v>0.07409581730613107</v>
+        <v>0.07464648445346225</v>
       </c>
     </row>
     <row r="290">
@@ -3303,7 +3303,7 @@
         </is>
       </c>
       <c r="B290" t="n">
-        <v>0.07615703476331999</v>
+        <v>0.06616878343225559</v>
       </c>
     </row>
     <row r="291">
@@ -3313,7 +3313,7 @@
         </is>
       </c>
       <c r="B291" t="n">
-        <v>0.04968710233953826</v>
+        <v>0.08584752131072616</v>
       </c>
     </row>
     <row r="292">
@@ -3323,7 +3323,7 @@
         </is>
       </c>
       <c r="B292" t="n">
-        <v>0.08419803043928986</v>
+        <v>0.06225880601859298</v>
       </c>
     </row>
     <row r="293">
@@ -3333,7 +3333,7 @@
         </is>
       </c>
       <c r="B293" t="n">
-        <v>0.1809970047623596</v>
+        <v>0.1934363031582823</v>
       </c>
     </row>
     <row r="294">
@@ -3343,7 +3343,7 @@
         </is>
       </c>
       <c r="B294" t="n">
-        <v>0.09034045686624417</v>
+        <v>0.08558569597854711</v>
       </c>
     </row>
     <row r="295">
@@ -3353,7 +3353,7 @@
         </is>
       </c>
       <c r="B295" t="n">
-        <v>0.01650470360519119</v>
+        <v>0.01567946842493163</v>
       </c>
     </row>
     <row r="296">
@@ -3363,7 +3363,7 @@
         </is>
       </c>
       <c r="B296" t="n">
-        <v>0.0694970707689237</v>
+        <v>0.06616391938374445</v>
       </c>
     </row>
     <row r="297">
@@ -3373,7 +3373,7 @@
         </is>
       </c>
       <c r="B297" t="n">
-        <v>0.07531660214491094</v>
+        <v>0.06952301736453317</v>
       </c>
     </row>
     <row r="298">
@@ -3383,7 +3383,7 @@
         </is>
       </c>
       <c r="B298" t="n">
-        <v>0.04462048367451854</v>
+        <v>0.06553612645991126</v>
       </c>
     </row>
     <row r="299">
@@ -3393,7 +3393,7 @@
         </is>
       </c>
       <c r="B299" t="n">
-        <v>0.1166568390858224</v>
+        <v>0.1040452889143821</v>
       </c>
     </row>
     <row r="300">
@@ -3403,7 +3403,7 @@
         </is>
       </c>
       <c r="B300" t="n">
-        <v>0.146372709057535</v>
+        <v>0.1503111038007348</v>
       </c>
     </row>
     <row r="301">
@@ -3413,7 +3413,7 @@
         </is>
       </c>
       <c r="B301" t="n">
-        <v>0.104643429540646</v>
+        <v>0.07583087666550956</v>
       </c>
     </row>
     <row r="302">
@@ -3423,7 +3423,7 @@
         </is>
       </c>
       <c r="B302" t="n">
-        <v>0.07197955441038066</v>
+        <v>0.0649571588581484</v>
       </c>
     </row>
     <row r="303">
@@ -3433,7 +3433,7 @@
         </is>
       </c>
       <c r="B303" t="n">
-        <v>0.03478580328101928</v>
+        <v>0.03512700996305018</v>
       </c>
     </row>
     <row r="304">
@@ -3453,7 +3453,7 @@
         </is>
       </c>
       <c r="B305" t="n">
-        <v>0.2994256830640449</v>
+        <v>0.2990633290874951</v>
       </c>
     </row>
     <row r="306">
@@ -3503,7 +3503,7 @@
         </is>
       </c>
       <c r="B310" t="n">
-        <v>0.09755247691547003</v>
+        <v>0.07960664382462621</v>
       </c>
     </row>
     <row r="311">
@@ -3523,7 +3523,7 @@
         </is>
       </c>
       <c r="B312" t="n">
-        <v>0.01579799357943643</v>
+        <v>0.01492032726946774</v>
       </c>
     </row>
     <row r="313">
@@ -3553,7 +3553,7 @@
         </is>
       </c>
       <c r="B315" t="n">
-        <v>0.1596734421187174</v>
+        <v>0.06780574227431783</v>
       </c>
     </row>
     <row r="316">
@@ -3563,7 +3563,7 @@
         </is>
       </c>
       <c r="B316" t="n">
-        <v>0.08641479117562131</v>
+        <v>0.1043834295664304</v>
       </c>
     </row>
     <row r="317">
@@ -3573,7 +3573,7 @@
         </is>
       </c>
       <c r="B317" t="n">
-        <v>0.07862441002294601</v>
+        <v>0.07822777547086589</v>
       </c>
     </row>
     <row r="318">
@@ -3593,7 +3593,7 @@
         </is>
       </c>
       <c r="B319" t="n">
-        <v>0.1038854019843019</v>
+        <v>0.06913362510807607</v>
       </c>
     </row>
     <row r="320">
@@ -3603,7 +3603,7 @@
         </is>
       </c>
       <c r="B320" t="n">
-        <v>0.02471510600562912</v>
+        <v>0.0270531522423967</v>
       </c>
     </row>
     <row r="321">
@@ -3613,7 +3613,7 @@
         </is>
       </c>
       <c r="B321" t="n">
-        <v>0.04293090616788855</v>
+        <v>0.07730774109598718</v>
       </c>
     </row>
     <row r="322">
@@ -3623,7 +3623,7 @@
         </is>
       </c>
       <c r="B322" t="n">
-        <v>0.1319006749407441</v>
+        <v>0.1545241588104194</v>
       </c>
     </row>
     <row r="323">
@@ -3633,7 +3633,7 @@
         </is>
       </c>
       <c r="B323" t="n">
-        <v>0.01691144772732672</v>
+        <v>0.01862828207118615</v>
       </c>
     </row>
     <row r="324">
@@ -3643,7 +3643,7 @@
         </is>
       </c>
       <c r="B324" t="n">
-        <v>0.1100389702100995</v>
+        <v>0.1371475168900045</v>
       </c>
     </row>
     <row r="325">
@@ -3653,7 +3653,7 @@
         </is>
       </c>
       <c r="B325" t="n">
-        <v>0.1680680545080576</v>
+        <v>0.2150037306560495</v>
       </c>
     </row>
     <row r="326">
@@ -3663,7 +3663,7 @@
         </is>
       </c>
       <c r="B326" t="n">
-        <v>0.09156848192009114</v>
+        <v>0.09866934985393373</v>
       </c>
     </row>
     <row r="327">
@@ -3693,7 +3693,7 @@
         </is>
       </c>
       <c r="B329" t="n">
-        <v>0.1134859666154355</v>
+        <v>0.08608265140683401</v>
       </c>
     </row>
     <row r="330">
@@ -3713,7 +3713,7 @@
         </is>
       </c>
       <c r="B331" t="n">
-        <v>0.08517202253492197</v>
+        <v>0.09091847095125563</v>
       </c>
     </row>
     <row r="332">
@@ -3723,7 +3723,7 @@
         </is>
       </c>
       <c r="B332" t="n">
-        <v>0.042810565146679</v>
+        <v>0.03957060391620788</v>
       </c>
     </row>
     <row r="333">
@@ -3773,7 +3773,7 @@
         </is>
       </c>
       <c r="B337" t="n">
-        <v>0.07142346537407659</v>
+        <v>0.08507457959973511</v>
       </c>
     </row>
     <row r="338">
@@ -3783,7 +3783,7 @@
         </is>
       </c>
       <c r="B338" t="n">
-        <v>0.1639397170964482</v>
+        <v>0.08446813833447582</v>
       </c>
     </row>
     <row r="339">
@@ -3793,7 +3793,7 @@
         </is>
       </c>
       <c r="B339" t="n">
-        <v>0.1905667648811321</v>
+        <v>0.1965516646378216</v>
       </c>
     </row>
     <row r="340">
@@ -3803,7 +3803,7 @@
         </is>
       </c>
       <c r="B340" t="n">
-        <v>0.03033949907490745</v>
+        <v>0.06805506014529107</v>
       </c>
     </row>
     <row r="341">
@@ -3823,7 +3823,7 @@
         </is>
       </c>
       <c r="B342" t="n">
-        <v>0.06487548317411407</v>
+        <v>0.04290506054838621</v>
       </c>
     </row>
     <row r="343">
@@ -3861,7 +3861,7 @@
         </is>
       </c>
       <c r="B346" t="n">
-        <v>0.1779590339614076</v>
+        <v>0.1663171932563019</v>
       </c>
     </row>
     <row r="347">
@@ -3871,7 +3871,7 @@
         </is>
       </c>
       <c r="B347" t="n">
-        <v>0.09927719329177208</v>
+        <v>0.09556187904434678</v>
       </c>
     </row>
     <row r="348">
@@ -3881,7 +3881,7 @@
         </is>
       </c>
       <c r="B348" t="n">
-        <v>0.02715743862667262</v>
+        <v>0</v>
       </c>
     </row>
     <row r="349">
@@ -3901,7 +3901,7 @@
         </is>
       </c>
       <c r="B350" t="n">
-        <v>0.02319837491868808</v>
+        <v>0.02046915434001889</v>
       </c>
     </row>
     <row r="351">
@@ -3921,7 +3921,7 @@
         </is>
       </c>
       <c r="B352" t="n">
-        <v>0.01453482466682297</v>
+        <v>0.01294496436148429</v>
       </c>
     </row>
     <row r="353">
@@ -3951,7 +3951,7 @@
         </is>
       </c>
       <c r="B355" t="n">
-        <v>0.02997848061184951</v>
+        <v>0.03172144260277259</v>
       </c>
     </row>
     <row r="356">
@@ -3961,7 +3961,7 @@
         </is>
       </c>
       <c r="B356" t="n">
-        <v>0.021763145750474</v>
+        <v>0.03537655530075686</v>
       </c>
     </row>
     <row r="357">
@@ -3971,7 +3971,7 @@
         </is>
       </c>
       <c r="B357" t="n">
-        <v>0.06348993869843399</v>
+        <v>0.05223316704283627</v>
       </c>
     </row>
     <row r="358">
@@ -4011,7 +4011,7 @@
         </is>
       </c>
       <c r="B361" t="n">
-        <v>0.1764819446992061</v>
+        <v>0.1762512797222832</v>
       </c>
     </row>
     <row r="362">
@@ -4051,7 +4051,7 @@
         </is>
       </c>
       <c r="B365" t="n">
-        <v>0.08953846579862106</v>
+        <v>0.07163915218158796</v>
       </c>
     </row>
     <row r="366">
@@ -4061,7 +4061,7 @@
         </is>
       </c>
       <c r="B366" t="n">
-        <v>0.1295748202614657</v>
+        <v>0.1300194933561499</v>
       </c>
     </row>
     <row r="367">
@@ -4079,7 +4079,7 @@
         </is>
       </c>
       <c r="B368" t="n">
-        <v>0.02540559300010822</v>
+        <v>0.01893311009307609</v>
       </c>
     </row>
     <row r="369">
@@ -4099,7 +4099,7 @@
         </is>
       </c>
       <c r="B370" t="n">
-        <v>0.06278124492132607</v>
+        <v>0.0675977341348783</v>
       </c>
     </row>
     <row r="371">
@@ -4109,7 +4109,7 @@
         </is>
       </c>
       <c r="B371" t="n">
-        <v>0.03089927235960686</v>
+        <v>0.06098368072906391</v>
       </c>
     </row>
     <row r="372">
@@ -4119,7 +4119,7 @@
         </is>
       </c>
       <c r="B372" t="n">
-        <v>0.1075327729254402</v>
+        <v>0.1134183684750844</v>
       </c>
     </row>
     <row r="373">
@@ -4129,7 +4129,7 @@
         </is>
       </c>
       <c r="B373" t="n">
-        <v>0.08947599907535864</v>
+        <v>0.05859333488521323</v>
       </c>
     </row>
     <row r="374">
@@ -4139,7 +4139,7 @@
         </is>
       </c>
       <c r="B374" t="n">
-        <v>0.08384409734962207</v>
+        <v>0.01830448615101303</v>
       </c>
     </row>
     <row r="375">
@@ -4149,7 +4149,7 @@
         </is>
       </c>
       <c r="B375" t="n">
-        <v>0.1513952110995257</v>
+        <v>0.1582325626656656</v>
       </c>
     </row>
     <row r="376">
@@ -4159,7 +4159,7 @@
         </is>
       </c>
       <c r="B376" t="n">
-        <v>0.1639302670744302</v>
+        <v>0.1569160803800217</v>
       </c>
     </row>
     <row r="377">
@@ -4179,7 +4179,7 @@
         </is>
       </c>
       <c r="B378" t="n">
-        <v>0.1359956859024539</v>
+        <v>0.01099875876231123</v>
       </c>
     </row>
     <row r="379">
@@ -4189,7 +4189,7 @@
         </is>
       </c>
       <c r="B379" t="n">
-        <v>0.05007995302225453</v>
+        <v>0.06177545979661851</v>
       </c>
     </row>
     <row r="380">
@@ -4219,7 +4219,7 @@
         </is>
       </c>
       <c r="B382" t="n">
-        <v>0.01359104638386467</v>
+        <v>0.02991571363939376</v>
       </c>
     </row>
     <row r="383">
@@ -4239,7 +4239,7 @@
         </is>
       </c>
       <c r="B384" t="n">
-        <v>0.1244301873208382</v>
+        <v>0.1360246189915116</v>
       </c>
     </row>
     <row r="385">
@@ -4259,7 +4259,7 @@
         </is>
       </c>
       <c r="B386" t="n">
-        <v>0.1224061469290277</v>
+        <v>0.1273009787812747</v>
       </c>
     </row>
     <row r="387">
@@ -4299,7 +4299,7 @@
         </is>
       </c>
       <c r="B390" t="n">
-        <v>0.1715223595367794</v>
+        <v>0.1587482328428312</v>
       </c>
     </row>
     <row r="391">
@@ -4329,7 +4329,7 @@
         </is>
       </c>
       <c r="B393" t="n">
-        <v>0.09955535775115838</v>
+        <v>0.09488106990674892</v>
       </c>
     </row>
     <row r="394">
@@ -4347,7 +4347,7 @@
         </is>
       </c>
       <c r="B395" t="n">
-        <v>0.05560256744573307</v>
+        <v>0.0535432130958911</v>
       </c>
     </row>
     <row r="396">
@@ -4357,7 +4357,7 @@
         </is>
       </c>
       <c r="B396" t="n">
-        <v>0.1395573901565569</v>
+        <v>0.1671392147468322</v>
       </c>
     </row>
     <row r="397">
@@ -4367,7 +4367,7 @@
         </is>
       </c>
       <c r="B397" t="n">
-        <v>0.04734960609227376</v>
+        <v>0.1103065714190774</v>
       </c>
     </row>
     <row r="398">
@@ -4387,7 +4387,7 @@
         </is>
       </c>
       <c r="B399" t="n">
-        <v>0.07653633803569272</v>
+        <v>0.07370956491839836</v>
       </c>
     </row>
     <row r="400">
@@ -4407,7 +4407,7 @@
         </is>
       </c>
       <c r="B401" t="n">
-        <v>0.1850116221777134</v>
+        <v>0.1676696518013656</v>
       </c>
     </row>
     <row r="402">
@@ -4457,7 +4457,7 @@
         </is>
       </c>
       <c r="B406" t="n">
-        <v>0.1539745759018078</v>
+        <v>0.1405332437547643</v>
       </c>
     </row>
     <row r="407">
@@ -4497,7 +4497,7 @@
         </is>
       </c>
       <c r="B410" t="n">
-        <v>0.0333912932013816</v>
+        <v>0.06609999862094176</v>
       </c>
     </row>
     <row r="411">
@@ -4507,7 +4507,7 @@
         </is>
       </c>
       <c r="B411" t="n">
-        <v>0.04235202876906946</v>
+        <v>0.0600302220307776</v>
       </c>
     </row>
     <row r="412">
@@ -4517,7 +4517,7 @@
         </is>
       </c>
       <c r="B412" t="n">
-        <v>0.05099690131915107</v>
+        <v>0.0586950116533708</v>
       </c>
     </row>
     <row r="413">
@@ -4577,7 +4577,7 @@
         </is>
       </c>
       <c r="B418" t="n">
-        <v>0.2379143510890591</v>
+        <v>0.2307559570081736</v>
       </c>
     </row>
     <row r="419">
@@ -4597,7 +4597,7 @@
         </is>
       </c>
       <c r="B420" t="n">
-        <v>0.1408487541856351</v>
+        <v>0.1336251663619753</v>
       </c>
     </row>
     <row r="421">
@@ -4627,7 +4627,7 @@
         </is>
       </c>
       <c r="B423" t="n">
-        <v>0.04646195938282898</v>
+        <v>0.05876321812159222</v>
       </c>
     </row>
     <row r="424">
@@ -4637,7 +4637,7 @@
         </is>
       </c>
       <c r="B424" t="n">
-        <v>0.06170957961681348</v>
+        <v>0.04304566956911923</v>
       </c>
     </row>
     <row r="425">
@@ -4657,7 +4657,7 @@
         </is>
       </c>
       <c r="B426" t="n">
-        <v>0.1191257905569458</v>
+        <v>0.1308616333985118</v>
       </c>
     </row>
     <row r="427">
@@ -4697,7 +4697,7 @@
         </is>
       </c>
       <c r="B430" t="n">
-        <v>0.03957209148069887</v>
+        <v>0.03749084515344817</v>
       </c>
     </row>
     <row r="431">
@@ -4717,7 +4717,7 @@
         </is>
       </c>
       <c r="B432" t="n">
-        <v>0.07714122624311331</v>
+        <v>0.07687590316479478</v>
       </c>
     </row>
     <row r="433">
@@ -4727,7 +4727,7 @@
         </is>
       </c>
       <c r="B433" t="n">
-        <v>0.02536161773679851</v>
+        <v>0.02780528013635072</v>
       </c>
     </row>
     <row r="434">
@@ -4737,7 +4737,7 @@
         </is>
       </c>
       <c r="B434" t="n">
-        <v>0.1117320363168661</v>
+        <v>0.1104847917385279</v>
       </c>
     </row>
     <row r="435">
@@ -4747,7 +4747,7 @@
         </is>
       </c>
       <c r="B435" t="n">
-        <v>0.01264670944303062</v>
+        <v>0.0154460310837434</v>
       </c>
     </row>
     <row r="436">
@@ -4767,7 +4767,7 @@
         </is>
       </c>
       <c r="B437" t="n">
-        <v>0.06174320049930266</v>
+        <v>0.04832076560814991</v>
       </c>
     </row>
     <row r="438">
@@ -4777,7 +4777,7 @@
         </is>
       </c>
       <c r="B438" t="n">
-        <v>0.2482456022989252</v>
+        <v>0.2142550577925915</v>
       </c>
     </row>
     <row r="439">
@@ -4797,7 +4797,7 @@
         </is>
       </c>
       <c r="B440" t="n">
-        <v>0.1757679226911257</v>
+        <v>0.1978212920745512</v>
       </c>
     </row>
     <row r="441">
@@ -4817,7 +4817,7 @@
         </is>
       </c>
       <c r="B442" t="n">
-        <v>0.08342510639457644</v>
+        <v>0.07961765739203328</v>
       </c>
     </row>
     <row r="443">
@@ -4827,7 +4827,7 @@
         </is>
       </c>
       <c r="B443" t="n">
-        <v>0.08046519578066015</v>
+        <v>0.09110161555122698</v>
       </c>
     </row>
     <row r="444">
@@ -4847,7 +4847,7 @@
         </is>
       </c>
       <c r="B445" t="n">
-        <v>0.1285471981352578</v>
+        <v>0.09232232806826418</v>
       </c>
     </row>
     <row r="446">
@@ -4857,7 +4857,7 @@
         </is>
       </c>
       <c r="B446" t="n">
-        <v>0.04158475654879223</v>
+        <v>0.03905909992528339</v>
       </c>
     </row>
     <row r="447">
@@ -4867,7 +4867,7 @@
         </is>
       </c>
       <c r="B447" t="n">
-        <v>0.1885427943324166</v>
+        <v>0.1509392066849256</v>
       </c>
     </row>
     <row r="448">
@@ -4877,7 +4877,7 @@
         </is>
       </c>
       <c r="B448" t="n">
-        <v>0.07623865106259084</v>
+        <v>0.09120122695824114</v>
       </c>
     </row>
     <row r="449">
@@ -4897,7 +4897,7 @@
         </is>
       </c>
       <c r="B450" t="n">
-        <v>0.01555044444207819</v>
+        <v>0.01332895237892416</v>
       </c>
     </row>
     <row r="451">
@@ -4927,7 +4927,7 @@
         </is>
       </c>
       <c r="B453" t="n">
-        <v>0.02496589245983344</v>
+        <v>0.03959483358244819</v>
       </c>
     </row>
     <row r="454">
@@ -4945,7 +4945,7 @@
         </is>
       </c>
       <c r="B455" t="n">
-        <v>0.1629965612877652</v>
+        <v>0.1340620333565985</v>
       </c>
     </row>
     <row r="456">
@@ -4955,7 +4955,7 @@
         </is>
       </c>
       <c r="B456" t="n">
-        <v>0.01355656005553068</v>
+        <v>0.03744601397670317</v>
       </c>
     </row>
     <row r="457">
@@ -4965,7 +4965,7 @@
         </is>
       </c>
       <c r="B457" t="n">
-        <v>0.08987536275426532</v>
+        <v>0.09019114347179003</v>
       </c>
     </row>
     <row r="458">
@@ -4975,7 +4975,7 @@
         </is>
       </c>
       <c r="B458" t="n">
-        <v>0.03575688265413423</v>
+        <v>0.04478212676317846</v>
       </c>
     </row>
     <row r="459">
@@ -5025,7 +5025,7 @@
         </is>
       </c>
       <c r="B463" t="n">
-        <v>0.07323684472739267</v>
+        <v>0.08627717291349171</v>
       </c>
     </row>
     <row r="464">
@@ -5045,7 +5045,7 @@
         </is>
       </c>
       <c r="B465" t="n">
-        <v>0.04274142365115145</v>
+        <v>0.07460681773004486</v>
       </c>
     </row>
     <row r="466">
@@ -5085,7 +5085,7 @@
         </is>
       </c>
       <c r="B469" t="n">
-        <v>0.1285223150595582</v>
+        <v>0.1134020426996102</v>
       </c>
     </row>
     <row r="470">
@@ -5105,7 +5105,7 @@
         </is>
       </c>
       <c r="B471" t="n">
-        <v>0.1711052087511566</v>
+        <v>0.1952105693703184</v>
       </c>
     </row>
     <row r="472">
@@ -5115,7 +5115,7 @@
         </is>
       </c>
       <c r="B472" t="n">
-        <v>0.07243738496421349</v>
+        <v>0.0699178192186023</v>
       </c>
     </row>
     <row r="473">
@@ -5125,7 +5125,7 @@
         </is>
       </c>
       <c r="B473" t="n">
-        <v>0.08876597067480822</v>
+        <v>0.0790775083285709</v>
       </c>
     </row>
     <row r="474">
@@ -5145,7 +5145,7 @@
         </is>
       </c>
       <c r="B475" t="n">
-        <v>0.207497161369204</v>
+        <v>0.08421606452113223</v>
       </c>
     </row>
     <row r="476">
@@ -5165,7 +5165,7 @@
         </is>
       </c>
       <c r="B477" t="n">
-        <v>0.1643754806404594</v>
+        <v>0.204039887407361</v>
       </c>
     </row>
     <row r="478">
@@ -5185,7 +5185,7 @@
         </is>
       </c>
       <c r="B479" t="n">
-        <v>0.223307292035405</v>
+        <v>0.2332699524907672</v>
       </c>
     </row>
     <row r="480">
@@ -5195,7 +5195,7 @@
         </is>
       </c>
       <c r="B480" t="n">
-        <v>0.1223689455982712</v>
+        <v>0.1194018113212649</v>
       </c>
     </row>
     <row r="481">
@@ -5205,7 +5205,7 @@
         </is>
       </c>
       <c r="B481" t="n">
-        <v>0.1451116190602609</v>
+        <v>0.1404797474049164</v>
       </c>
     </row>
     <row r="482">
@@ -5235,7 +5235,7 @@
         </is>
       </c>
       <c r="B484" t="n">
-        <v>0.04514260027218688</v>
+        <v>0.04867634566657204</v>
       </c>
     </row>
     <row r="485">
@@ -5245,7 +5245,7 @@
         </is>
       </c>
       <c r="B485" t="n">
-        <v>0.1367985455750081</v>
+        <v>0.1443853521959526</v>
       </c>
     </row>
   </sheetData>

--- a/gemini/evaluation_results/iou_scores.xlsx
+++ b/gemini/evaluation_results/iou_scores.xlsx
@@ -447,7 +447,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.06051764764664517</v>
+        <v>0.1285851796438157</v>
       </c>
     </row>
     <row r="3">
@@ -457,7 +457,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.1921962538172182</v>
+        <v>0.2514108560837044</v>
       </c>
     </row>
     <row r="4">
@@ -467,7 +467,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.07099336486228139</v>
+        <v>0.2436719602283492</v>
       </c>
     </row>
     <row r="5">
@@ -477,7 +477,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.1038174681367415</v>
+        <v>0.3396881571084652</v>
       </c>
     </row>
     <row r="6">
@@ -487,7 +487,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.3351129338893953</v>
+        <v>0.4365295920429542</v>
       </c>
     </row>
     <row r="7">
@@ -497,7 +497,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.1781396107389369</v>
+        <v>0.214397011310723</v>
       </c>
     </row>
     <row r="8">
@@ -507,7 +507,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.007148713899602175</v>
+        <v>0.09051731270740042</v>
       </c>
     </row>
     <row r="9">
@@ -517,7 +517,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.0640237734082757</v>
+        <v>0.171010828579844</v>
       </c>
     </row>
     <row r="10">
@@ -527,7 +527,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.091825929729472</v>
+        <v>0.1640246881438863</v>
       </c>
     </row>
     <row r="11">
@@ -537,7 +537,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.0740592933793416</v>
+        <v>0.126401271386694</v>
       </c>
     </row>
     <row r="12">
@@ -547,7 +547,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.1729772797583757</v>
+        <v>0.2979134372499595</v>
       </c>
     </row>
     <row r="13">
@@ -565,7 +565,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.2374279305055407</v>
+        <v>0.350850972298791</v>
       </c>
     </row>
     <row r="15">
@@ -585,7 +585,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.05596733647051951</v>
+        <v>0.1500590958286595</v>
       </c>
     </row>
     <row r="17">
@@ -595,7 +595,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.1483516483516484</v>
+        <v>0.1965389079234791</v>
       </c>
     </row>
     <row r="18">
@@ -605,7 +605,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.1239527950760973</v>
+        <v>0.1685926352782345</v>
       </c>
     </row>
     <row r="19">
@@ -625,7 +625,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.155696433409108</v>
+        <v>0.2682245128290682</v>
       </c>
     </row>
     <row r="21">
@@ -655,7 +655,7 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.01513687076302941</v>
+        <v>0.09959905964051502</v>
       </c>
     </row>
     <row r="24">
@@ -665,7 +665,7 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.2360090038329747</v>
+        <v>0.2104130791519365</v>
       </c>
     </row>
     <row r="25">
@@ -675,7 +675,7 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.1616360026038227</v>
+        <v>0.260845298842552</v>
       </c>
     </row>
     <row r="26">
@@ -685,7 +685,7 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.08189362107800345</v>
+        <v>0.1490034149152312</v>
       </c>
     </row>
     <row r="27">
@@ -695,7 +695,7 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.1569078967806601</v>
+        <v>0.188102296165171</v>
       </c>
     </row>
     <row r="28">
@@ -705,7 +705,7 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.02915684764768806</v>
+        <v>0.09001485945491107</v>
       </c>
     </row>
     <row r="29">
@@ -715,7 +715,7 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.06748371288711906</v>
+        <v>0.2197029142129952</v>
       </c>
     </row>
     <row r="30">
@@ -725,7 +725,7 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0.09201058911413997</v>
+        <v>0.2117592274122122</v>
       </c>
     </row>
     <row r="31">
@@ -735,7 +735,7 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0.03832366836449593</v>
+        <v>0.2038628052798911</v>
       </c>
     </row>
     <row r="32">
@@ -753,7 +753,7 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>0.1257645656456247</v>
+        <v>0.2678863038223706</v>
       </c>
     </row>
     <row r="34">
@@ -773,7 +773,7 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>0.2221969898592428</v>
+        <v>0.2650753547472408</v>
       </c>
     </row>
     <row r="36">
@@ -783,7 +783,7 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>0.08382432997509907</v>
+        <v>0.2276204103377299</v>
       </c>
     </row>
     <row r="37">
@@ -793,7 +793,7 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>0.06150948695094036</v>
+        <v>0.130452048861262</v>
       </c>
     </row>
     <row r="38">
@@ -803,7 +803,7 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>0.1087226477258045</v>
+        <v>0.254811559309057</v>
       </c>
     </row>
     <row r="39">
@@ -813,7 +813,7 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>0.0872329559945496</v>
+        <v>0.247517707067554</v>
       </c>
     </row>
     <row r="40">
@@ -823,7 +823,7 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>0.04188433728689261</v>
+        <v>0.1558651527224924</v>
       </c>
     </row>
     <row r="41">
@@ -833,7 +833,7 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>0.1413718076563293</v>
+        <v>0.270407858839194</v>
       </c>
     </row>
     <row r="42">
@@ -861,7 +861,7 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>0.2185978781903138</v>
+        <v>0.2590826908550043</v>
       </c>
     </row>
     <row r="45">
@@ -871,7 +871,7 @@
         </is>
       </c>
       <c r="B45" t="n">
-        <v>0.07946158195041761</v>
+        <v>0.166000783063821</v>
       </c>
     </row>
     <row r="46">
@@ -891,7 +891,7 @@
         </is>
       </c>
       <c r="B47" t="n">
-        <v>0.05020861662669689</v>
+        <v>0.1407756819696985</v>
       </c>
     </row>
     <row r="48">
@@ -911,7 +911,7 @@
         </is>
       </c>
       <c r="B49" t="n">
-        <v>0.0503644650054764</v>
+        <v>0.1582168042807471</v>
       </c>
     </row>
     <row r="50">
@@ -921,7 +921,7 @@
         </is>
       </c>
       <c r="B50" t="n">
-        <v>0.05426067099092422</v>
+        <v>0.1202102301859661</v>
       </c>
     </row>
     <row r="51">
@@ -931,7 +931,7 @@
         </is>
       </c>
       <c r="B51" t="n">
-        <v>0.1032694836097124</v>
+        <v>0.1784592659242835</v>
       </c>
     </row>
     <row r="52">
@@ -967,7 +967,7 @@
         </is>
       </c>
       <c r="B55" t="n">
-        <v>0.09925477522439713</v>
+        <v>0.1631784386399248</v>
       </c>
     </row>
     <row r="56">
@@ -977,7 +977,7 @@
         </is>
       </c>
       <c r="B56" t="n">
-        <v>0.04009178037816191</v>
+        <v>0.1794277156585286</v>
       </c>
     </row>
     <row r="57">
@@ -987,7 +987,7 @@
         </is>
       </c>
       <c r="B57" t="n">
-        <v>0.1317626132751147</v>
+        <v>0.1607323127272711</v>
       </c>
     </row>
     <row r="58">
@@ -997,7 +997,7 @@
         </is>
       </c>
       <c r="B58" t="n">
-        <v>0</v>
+        <v>0.2545429955834028</v>
       </c>
     </row>
     <row r="59">
@@ -1007,7 +1007,7 @@
         </is>
       </c>
       <c r="B59" t="n">
-        <v>0.03813744334555278</v>
+        <v>0.1653340119214355</v>
       </c>
     </row>
     <row r="60">
@@ -1017,7 +1017,7 @@
         </is>
       </c>
       <c r="B60" t="n">
-        <v>0.0862557070616468</v>
+        <v>0.2058731036839375</v>
       </c>
     </row>
     <row r="61">
@@ -1027,7 +1027,7 @@
         </is>
       </c>
       <c r="B61" t="n">
-        <v>0.1473103804324892</v>
+        <v>0.2949872891889622</v>
       </c>
     </row>
     <row r="62">
@@ -1037,7 +1037,7 @@
         </is>
       </c>
       <c r="B62" t="n">
-        <v>0.01573472086818887</v>
+        <v>0.09564492588967898</v>
       </c>
     </row>
     <row r="63">
@@ -1047,7 +1047,7 @@
         </is>
       </c>
       <c r="B63" t="n">
-        <v>0.1259669834081098</v>
+        <v>0.1833683564816375</v>
       </c>
     </row>
     <row r="64">
@@ -1067,7 +1067,7 @@
         </is>
       </c>
       <c r="B65" t="n">
-        <v>0.1689714606887595</v>
+        <v>0.2936891211210407</v>
       </c>
     </row>
     <row r="66">
@@ -1077,7 +1077,7 @@
         </is>
       </c>
       <c r="B66" t="n">
-        <v>0</v>
+        <v>0.01292246730168355</v>
       </c>
     </row>
     <row r="67">
@@ -1087,7 +1087,7 @@
         </is>
       </c>
       <c r="B67" t="n">
-        <v>0.05291714374097532</v>
+        <v>0.158624378857904</v>
       </c>
     </row>
     <row r="68">
@@ -1097,7 +1097,7 @@
         </is>
       </c>
       <c r="B68" t="n">
-        <v>0.04227007759741044</v>
+        <v>0.2096096007084857</v>
       </c>
     </row>
     <row r="69">
@@ -1107,7 +1107,7 @@
         </is>
       </c>
       <c r="B69" t="n">
-        <v>0.06966140087854034</v>
+        <v>0.1539370354053453</v>
       </c>
     </row>
     <row r="70">
@@ -1117,7 +1117,7 @@
         </is>
       </c>
       <c r="B70" t="n">
-        <v>0.07923277295224335</v>
+        <v>0.1833657991020446</v>
       </c>
     </row>
     <row r="71">
@@ -1127,7 +1127,7 @@
         </is>
       </c>
       <c r="B71" t="n">
-        <v>0.02443272349811004</v>
+        <v>0.06575325267825056</v>
       </c>
     </row>
     <row r="72">
@@ -1147,7 +1147,7 @@
         </is>
       </c>
       <c r="B73" t="n">
-        <v>0.08085722513410486</v>
+        <v>0.2420094845028611</v>
       </c>
     </row>
     <row r="74">
@@ -1157,7 +1157,7 @@
         </is>
       </c>
       <c r="B74" t="n">
-        <v>0.08645526899340381</v>
+        <v>0.1859750775412444</v>
       </c>
     </row>
     <row r="75">
@@ -1177,7 +1177,7 @@
         </is>
       </c>
       <c r="B76" t="n">
-        <v>0.1197478045905175</v>
+        <v>0.2558521465977234</v>
       </c>
     </row>
     <row r="77">
@@ -1187,7 +1187,7 @@
         </is>
       </c>
       <c r="B77" t="n">
-        <v>0.1198979703178258</v>
+        <v>0.1979059854510579</v>
       </c>
     </row>
     <row r="78">
@@ -1197,7 +1197,7 @@
         </is>
       </c>
       <c r="B78" t="n">
-        <v>0.09517047362818983</v>
+        <v>0.2015401932991428</v>
       </c>
     </row>
     <row r="79">
@@ -1207,7 +1207,7 @@
         </is>
       </c>
       <c r="B79" t="n">
-        <v>0.1396396529351549</v>
+        <v>0.1560829022393334</v>
       </c>
     </row>
     <row r="80">
@@ -1217,7 +1217,7 @@
         </is>
       </c>
       <c r="B80" t="n">
-        <v>0.130826280669198</v>
+        <v>0.1232479397871792</v>
       </c>
     </row>
     <row r="81">
@@ -1227,7 +1227,7 @@
         </is>
       </c>
       <c r="B81" t="n">
-        <v>0.02359801769967381</v>
+        <v>0.110810449935167</v>
       </c>
     </row>
     <row r="82">
@@ -1237,7 +1237,7 @@
         </is>
       </c>
       <c r="B82" t="n">
-        <v>0.1203965677755821</v>
+        <v>0.161513079841805</v>
       </c>
     </row>
     <row r="83">
@@ -1247,7 +1247,7 @@
         </is>
       </c>
       <c r="B83" t="n">
-        <v>0.06708030534637904</v>
+        <v>0.2584319391111006</v>
       </c>
     </row>
     <row r="84">
@@ -1257,7 +1257,7 @@
         </is>
       </c>
       <c r="B84" t="n">
-        <v>0.03543941077999858</v>
+        <v>0.175840517336224</v>
       </c>
     </row>
     <row r="85">
@@ -1277,7 +1277,7 @@
         </is>
       </c>
       <c r="B86" t="n">
-        <v>0.02292368745330779</v>
+        <v>0.04117979908624348</v>
       </c>
     </row>
     <row r="87">
@@ -1287,7 +1287,7 @@
         </is>
       </c>
       <c r="B87" t="n">
-        <v>0.05559804002399343</v>
+        <v>0.1867897652975825</v>
       </c>
     </row>
     <row r="88">
@@ -1297,7 +1297,7 @@
         </is>
       </c>
       <c r="B88" t="n">
-        <v>0.03576159207981704</v>
+        <v>0.139199837220185</v>
       </c>
     </row>
     <row r="89">
@@ -1307,7 +1307,7 @@
         </is>
       </c>
       <c r="B89" t="n">
-        <v>0.1024279807870987</v>
+        <v>0.2613049772948624</v>
       </c>
     </row>
     <row r="90">
@@ -1317,7 +1317,7 @@
         </is>
       </c>
       <c r="B90" t="n">
-        <v>0.1178043064803409</v>
+        <v>0.179817234833142</v>
       </c>
     </row>
     <row r="91">
@@ -1327,7 +1327,7 @@
         </is>
       </c>
       <c r="B91" t="n">
-        <v>0.03572401191739306</v>
+        <v>0.2793427193668018</v>
       </c>
     </row>
     <row r="92">
@@ -1337,7 +1337,7 @@
         </is>
       </c>
       <c r="B92" t="n">
-        <v>0.01011309238200513</v>
+        <v>0.2400318679400465</v>
       </c>
     </row>
     <row r="93">
@@ -1355,7 +1355,7 @@
         </is>
       </c>
       <c r="B94" t="n">
-        <v>0.08969153334651728</v>
+        <v>0.1702611500071677</v>
       </c>
     </row>
     <row r="95">
@@ -1375,7 +1375,7 @@
         </is>
       </c>
       <c r="B96" t="n">
-        <v>0.2111814999926092</v>
+        <v>0.338256931202376</v>
       </c>
     </row>
     <row r="97">
@@ -1385,7 +1385,7 @@
         </is>
       </c>
       <c r="B97" t="n">
-        <v>0.07014165418390471</v>
+        <v>0.2866296303604894</v>
       </c>
     </row>
     <row r="98">
@@ -1395,7 +1395,7 @@
         </is>
       </c>
       <c r="B98" t="n">
-        <v>0.0182287099998906</v>
+        <v>0.09297055298570492</v>
       </c>
     </row>
     <row r="99">
@@ -1415,7 +1415,7 @@
         </is>
       </c>
       <c r="B100" t="n">
-        <v>0.06898373292213768</v>
+        <v>0.1453064461642134</v>
       </c>
     </row>
     <row r="101">
@@ -1455,7 +1455,7 @@
         </is>
       </c>
       <c r="B104" t="n">
-        <v>0.05298916120479725</v>
+        <v>0.1122342282052179</v>
       </c>
     </row>
     <row r="105">
@@ -1465,7 +1465,7 @@
         </is>
       </c>
       <c r="B105" t="n">
-        <v>0.1260725647787904</v>
+        <v>0.271457358908148</v>
       </c>
     </row>
     <row r="106">
@@ -1475,7 +1475,7 @@
         </is>
       </c>
       <c r="B106" t="n">
-        <v>0.07141852018381568</v>
+        <v>0.1754545678189973</v>
       </c>
     </row>
     <row r="107">
@@ -1485,7 +1485,7 @@
         </is>
       </c>
       <c r="B107" t="n">
-        <v>0.1329349974062483</v>
+        <v>0.285964471134968</v>
       </c>
     </row>
     <row r="108">
@@ -1495,7 +1495,7 @@
         </is>
       </c>
       <c r="B108" t="n">
-        <v>0.02611320170484037</v>
+        <v>0.1886349371269811</v>
       </c>
     </row>
     <row r="109">
@@ -1525,7 +1525,7 @@
         </is>
       </c>
       <c r="B111" t="n">
-        <v>0.1335288428167246</v>
+        <v>0.2654611718395165</v>
       </c>
     </row>
     <row r="112">
@@ -1535,7 +1535,7 @@
         </is>
       </c>
       <c r="B112" t="n">
-        <v>0.06274084204318291</v>
+        <v>0.09898968084961079</v>
       </c>
     </row>
     <row r="113">
@@ -1545,7 +1545,7 @@
         </is>
       </c>
       <c r="B113" t="n">
-        <v>0.07987908517291167</v>
+        <v>0.2078229403490749</v>
       </c>
     </row>
     <row r="114">
@@ -1555,7 +1555,7 @@
         </is>
       </c>
       <c r="B114" t="n">
-        <v>0.08572448353417721</v>
+        <v>0.17293183249143</v>
       </c>
     </row>
     <row r="115">
@@ -1565,7 +1565,7 @@
         </is>
       </c>
       <c r="B115" t="n">
-        <v>0.1818220088630532</v>
+        <v>0.393392405169378</v>
       </c>
     </row>
     <row r="116">
@@ -1585,7 +1585,7 @@
         </is>
       </c>
       <c r="B117" t="n">
-        <v>0.06995738125782008</v>
+        <v>0.1182390407495023</v>
       </c>
     </row>
     <row r="118">
@@ -1595,7 +1595,7 @@
         </is>
       </c>
       <c r="B118" t="n">
-        <v>0.06199242581056374</v>
+        <v>0.204924221570297</v>
       </c>
     </row>
     <row r="119">
@@ -1615,7 +1615,7 @@
         </is>
       </c>
       <c r="B120" t="n">
-        <v>0.01745719144073542</v>
+        <v>0.1428933708940244</v>
       </c>
     </row>
     <row r="121">
@@ -1625,7 +1625,7 @@
         </is>
       </c>
       <c r="B121" t="n">
-        <v>0.08241132314386299</v>
+        <v>0.1513866635579045</v>
       </c>
     </row>
     <row r="122">
@@ -1635,7 +1635,7 @@
         </is>
       </c>
       <c r="B122" t="n">
-        <v>0</v>
+        <v>0.08643062326028923</v>
       </c>
     </row>
     <row r="123">
@@ -1645,7 +1645,7 @@
         </is>
       </c>
       <c r="B123" t="n">
-        <v>0.02893452568976133</v>
+        <v>0.1412439661366535</v>
       </c>
     </row>
     <row r="124">
@@ -1663,7 +1663,7 @@
         </is>
       </c>
       <c r="B125" t="n">
-        <v>0.03624045849760908</v>
+        <v>0.3222184792847221</v>
       </c>
     </row>
     <row r="126">
@@ -1673,7 +1673,7 @@
         </is>
       </c>
       <c r="B126" t="n">
-        <v>0.01652967441715559</v>
+        <v>0.02438812039549993</v>
       </c>
     </row>
     <row r="127">
@@ -1683,7 +1683,7 @@
         </is>
       </c>
       <c r="B127" t="n">
-        <v>0.0572366446899022</v>
+        <v>0.1283956903104525</v>
       </c>
     </row>
     <row r="128">
@@ -1693,7 +1693,7 @@
         </is>
       </c>
       <c r="B128" t="n">
-        <v>0.08580871455022897</v>
+        <v>0.2111628010425559</v>
       </c>
     </row>
     <row r="129">
@@ -1703,7 +1703,7 @@
         </is>
       </c>
       <c r="B129" t="n">
-        <v>0.001071896409348766</v>
+        <v>0.09774933067337592</v>
       </c>
     </row>
     <row r="130">
@@ -1713,7 +1713,7 @@
         </is>
       </c>
       <c r="B130" t="n">
-        <v>0.07206080287405678</v>
+        <v>0.2022993768027002</v>
       </c>
     </row>
     <row r="131">
@@ -1723,7 +1723,7 @@
         </is>
       </c>
       <c r="B131" t="n">
-        <v>0.1832699622071891</v>
+        <v>0.1927324203021546</v>
       </c>
     </row>
     <row r="132">
@@ -1733,7 +1733,7 @@
         </is>
       </c>
       <c r="B132" t="n">
-        <v>0.11932952415937</v>
+        <v>0.1931543633111876</v>
       </c>
     </row>
     <row r="133">
@@ -1753,7 +1753,7 @@
         </is>
       </c>
       <c r="B134" t="n">
-        <v>0.08522623372406832</v>
+        <v>0.1800046751400041</v>
       </c>
     </row>
     <row r="135">
@@ -1763,7 +1763,7 @@
         </is>
       </c>
       <c r="B135" t="n">
-        <v>0.05814268362137383</v>
+        <v>0.1740734165152845</v>
       </c>
     </row>
     <row r="136">
@@ -1773,7 +1773,7 @@
         </is>
       </c>
       <c r="B136" t="n">
-        <v>0.1559354870932186</v>
+        <v>0.2447782188645854</v>
       </c>
     </row>
     <row r="137">
@@ -1783,7 +1783,7 @@
         </is>
       </c>
       <c r="B137" t="n">
-        <v>0.04794700900028918</v>
+        <v>0.1372008412233892</v>
       </c>
     </row>
     <row r="138">
@@ -1793,7 +1793,7 @@
         </is>
       </c>
       <c r="B138" t="n">
-        <v>0.0495985938613151</v>
+        <v>0.1600140739678939</v>
       </c>
     </row>
     <row r="139">
@@ -1803,7 +1803,7 @@
         </is>
       </c>
       <c r="B139" t="n">
-        <v>0.1566085320928998</v>
+        <v>0.3047653022882487</v>
       </c>
     </row>
     <row r="140">
@@ -1813,7 +1813,7 @@
         </is>
       </c>
       <c r="B140" t="n">
-        <v>0.08278529378006685</v>
+        <v>0.1794767499418789</v>
       </c>
     </row>
     <row r="141">
@@ -1823,7 +1823,7 @@
         </is>
       </c>
       <c r="B141" t="n">
-        <v>0.04956310539500655</v>
+        <v>0.1891244151289192</v>
       </c>
     </row>
     <row r="142">
@@ -1853,7 +1853,7 @@
         </is>
       </c>
       <c r="B144" t="n">
-        <v>0.04361255894471697</v>
+        <v>0.1092175823946076</v>
       </c>
     </row>
     <row r="145">
@@ -1863,7 +1863,7 @@
         </is>
       </c>
       <c r="B145" t="n">
-        <v>0.06160535024622639</v>
+        <v>0.1829914637857255</v>
       </c>
     </row>
     <row r="146">
@@ -1873,7 +1873,7 @@
         </is>
       </c>
       <c r="B146" t="n">
-        <v>0.05908640394889603</v>
+        <v>0.2291489974972601</v>
       </c>
     </row>
     <row r="147">
@@ -1883,7 +1883,7 @@
         </is>
       </c>
       <c r="B147" t="n">
-        <v>0.05936855007236539</v>
+        <v>0.1033245000727466</v>
       </c>
     </row>
     <row r="148">
@@ -1893,7 +1893,7 @@
         </is>
       </c>
       <c r="B148" t="n">
-        <v>0.07738546162733612</v>
+        <v>0.1769510776090649</v>
       </c>
     </row>
     <row r="149">
@@ -1911,7 +1911,7 @@
         </is>
       </c>
       <c r="B150" t="n">
-        <v>0.02613960191751631</v>
+        <v>0.09040839384170182</v>
       </c>
     </row>
     <row r="151">
@@ -1921,7 +1921,7 @@
         </is>
       </c>
       <c r="B151" t="n">
-        <v>0.1049429548582314</v>
+        <v>0.194888826172846</v>
       </c>
     </row>
     <row r="152">
@@ -1931,7 +1931,7 @@
         </is>
       </c>
       <c r="B152" t="n">
-        <v>0.2478349602999727</v>
+        <v>0.2592022840745042</v>
       </c>
     </row>
     <row r="153">
@@ -1971,7 +1971,7 @@
         </is>
       </c>
       <c r="B156" t="n">
-        <v>0.109221462994345</v>
+        <v>0.2464276426852416</v>
       </c>
     </row>
     <row r="157">
@@ -1991,7 +1991,7 @@
         </is>
       </c>
       <c r="B158" t="n">
-        <v>0.1031022975748596</v>
+        <v>0.2506133694012935</v>
       </c>
     </row>
     <row r="159">
@@ -2011,7 +2011,7 @@
         </is>
       </c>
       <c r="B160" t="n">
-        <v>0.1381730997553259</v>
+        <v>0.2407747388965134</v>
       </c>
     </row>
     <row r="161">
@@ -2021,7 +2021,7 @@
         </is>
       </c>
       <c r="B161" t="n">
-        <v>0.03454868403867413</v>
+        <v>0.06445317581587406</v>
       </c>
     </row>
     <row r="162">
@@ -2031,7 +2031,7 @@
         </is>
       </c>
       <c r="B162" t="n">
-        <v>0.2336675058123023</v>
+        <v>0.2996268502397162</v>
       </c>
     </row>
     <row r="163">
@@ -2079,7 +2079,7 @@
         </is>
       </c>
       <c r="B167" t="n">
-        <v>0.01541793685808208</v>
+        <v>0.07589530138989618</v>
       </c>
     </row>
     <row r="168">
@@ -2089,7 +2089,7 @@
         </is>
       </c>
       <c r="B168" t="n">
-        <v>0.1103814477936036</v>
+        <v>0.2611751653835693</v>
       </c>
     </row>
     <row r="169">
@@ -2099,7 +2099,7 @@
         </is>
       </c>
       <c r="B169" t="n">
-        <v>0.09167098674876856</v>
+        <v>0.1957115702399992</v>
       </c>
     </row>
     <row r="170">
@@ -2109,7 +2109,7 @@
         </is>
       </c>
       <c r="B170" t="n">
-        <v>0.01833353996514341</v>
+        <v>0.1492283693803096</v>
       </c>
     </row>
     <row r="171">
@@ -2119,7 +2119,7 @@
         </is>
       </c>
       <c r="B171" t="n">
-        <v>0.02056178981224652</v>
+        <v>0.08548164469032767</v>
       </c>
     </row>
     <row r="172">
@@ -2129,7 +2129,7 @@
         </is>
       </c>
       <c r="B172" t="n">
-        <v>0.1705674588846694</v>
+        <v>0.2301350199826452</v>
       </c>
     </row>
     <row r="173">
@@ -2139,7 +2139,7 @@
         </is>
       </c>
       <c r="B173" t="n">
-        <v>0.2341276139546641</v>
+        <v>0.22555016092393</v>
       </c>
     </row>
     <row r="174">
@@ -2159,7 +2159,7 @@
         </is>
       </c>
       <c r="B175" t="n">
-        <v>0.05326511687727591</v>
+        <v>0.32162250836014</v>
       </c>
     </row>
     <row r="176">
@@ -2169,7 +2169,7 @@
         </is>
       </c>
       <c r="B176" t="n">
-        <v>0.06514136401689244</v>
+        <v>0.1271552765395964</v>
       </c>
     </row>
     <row r="177">
@@ -2179,7 +2179,7 @@
         </is>
       </c>
       <c r="B177" t="n">
-        <v>0.02914739213748587</v>
+        <v>0.2168476232599702</v>
       </c>
     </row>
     <row r="178">
@@ -2189,7 +2189,7 @@
         </is>
       </c>
       <c r="B178" t="n">
-        <v>0.123264186557811</v>
+        <v>0.1798356560100898</v>
       </c>
     </row>
     <row r="179">
@@ -2199,7 +2199,7 @@
         </is>
       </c>
       <c r="B179" t="n">
-        <v>0.04526341045511535</v>
+        <v>0.149879260151505</v>
       </c>
     </row>
     <row r="180">
@@ -2219,7 +2219,7 @@
         </is>
       </c>
       <c r="B181" t="n">
-        <v>0.1348783448401431</v>
+        <v>0.2561104534578497</v>
       </c>
     </row>
     <row r="182">
@@ -2239,7 +2239,7 @@
         </is>
       </c>
       <c r="B183" t="n">
-        <v>0.2262948107840412</v>
+        <v>0.3448405667334635</v>
       </c>
     </row>
     <row r="184">
@@ -2249,7 +2249,7 @@
         </is>
       </c>
       <c r="B184" t="n">
-        <v>0.02544953802026633</v>
+        <v>0.1196680871005775</v>
       </c>
     </row>
     <row r="185">
@@ -2277,7 +2277,7 @@
         </is>
       </c>
       <c r="B187" t="n">
-        <v>0</v>
+        <v>0.07769409604826857</v>
       </c>
     </row>
     <row r="188">
@@ -2287,7 +2287,7 @@
         </is>
       </c>
       <c r="B188" t="n">
-        <v>0.3086284630288238</v>
+        <v>0.3640810706203477</v>
       </c>
     </row>
     <row r="189">
@@ -2307,7 +2307,7 @@
         </is>
       </c>
       <c r="B190" t="n">
-        <v>0.04646370155666172</v>
+        <v>0.2246743629164011</v>
       </c>
     </row>
     <row r="191">
@@ -2327,7 +2327,7 @@
         </is>
       </c>
       <c r="B192" t="n">
-        <v>0.05074053507888362</v>
+        <v>0.1754848715908169</v>
       </c>
     </row>
     <row r="193">
@@ -2337,7 +2337,7 @@
         </is>
       </c>
       <c r="B193" t="n">
-        <v>0.2492485294690917</v>
+        <v>0.2834107918782098</v>
       </c>
     </row>
     <row r="194">
@@ -2347,7 +2347,7 @@
         </is>
       </c>
       <c r="B194" t="n">
-        <v>0.02295852653714258</v>
+        <v>0.06243270510792447</v>
       </c>
     </row>
     <row r="195">
@@ -2357,7 +2357,7 @@
         </is>
       </c>
       <c r="B195" t="n">
-        <v>0.0346626611853188</v>
+        <v>0.1688309883129684</v>
       </c>
     </row>
     <row r="196">
@@ -2377,7 +2377,7 @@
         </is>
       </c>
       <c r="B197" t="n">
-        <v>0.09225130449807213</v>
+        <v>0.1707408233909281</v>
       </c>
     </row>
     <row r="198">
@@ -2397,7 +2397,7 @@
         </is>
       </c>
       <c r="B199" t="n">
-        <v>0</v>
+        <v>0.02934339139046286</v>
       </c>
     </row>
     <row r="200">
@@ -2407,7 +2407,7 @@
         </is>
       </c>
       <c r="B200" t="n">
-        <v>0.1069328960685775</v>
+        <v>0.1619710796725261</v>
       </c>
     </row>
     <row r="201">
@@ -2417,7 +2417,7 @@
         </is>
       </c>
       <c r="B201" t="n">
-        <v>0.08410881932206371</v>
+        <v>0.2196766411312659</v>
       </c>
     </row>
     <row r="202">
@@ -2427,7 +2427,7 @@
         </is>
       </c>
       <c r="B202" t="n">
-        <v>0.04585764788080155</v>
+        <v>0.09533829333296431</v>
       </c>
     </row>
     <row r="203">
@@ -2437,7 +2437,7 @@
         </is>
       </c>
       <c r="B203" t="n">
-        <v>0.03800560450736201</v>
+        <v>0.1070763606977668</v>
       </c>
     </row>
     <row r="204">
@@ -2447,7 +2447,7 @@
         </is>
       </c>
       <c r="B204" t="n">
-        <v>0.04759281457638095</v>
+        <v>0.2088998751091872</v>
       </c>
     </row>
     <row r="205">
@@ -2457,7 +2457,7 @@
         </is>
       </c>
       <c r="B205" t="n">
-        <v>0.03839286229174682</v>
+        <v>0.1135883020286264</v>
       </c>
     </row>
     <row r="206">
@@ -2467,7 +2467,7 @@
         </is>
       </c>
       <c r="B206" t="n">
-        <v>0.008159910898346582</v>
+        <v>0.03132090563710636</v>
       </c>
     </row>
     <row r="207">
@@ -2477,7 +2477,7 @@
         </is>
       </c>
       <c r="B207" t="n">
-        <v>0.07945166213868281</v>
+        <v>0.1828167717668409</v>
       </c>
     </row>
     <row r="208">
@@ -2487,7 +2487,7 @@
         </is>
       </c>
       <c r="B208" t="n">
-        <v>0.02767706756129282</v>
+        <v>0.1179976679865738</v>
       </c>
     </row>
     <row r="209">
@@ -2497,7 +2497,7 @@
         </is>
       </c>
       <c r="B209" t="n">
-        <v>0.05306411438358717</v>
+        <v>0.2065044211533338</v>
       </c>
     </row>
     <row r="210">
@@ -2507,7 +2507,7 @@
         </is>
       </c>
       <c r="B210" t="n">
-        <v>0.09127896327334821</v>
+        <v>0.256924357189565</v>
       </c>
     </row>
     <row r="211">
@@ -2517,7 +2517,7 @@
         </is>
       </c>
       <c r="B211" t="n">
-        <v>0.03548482022974128</v>
+        <v>0.1140369719620381</v>
       </c>
     </row>
     <row r="212">
@@ -2527,7 +2527,7 @@
         </is>
       </c>
       <c r="B212" t="n">
-        <v>0.1721322832967015</v>
+        <v>0.2764135093668292</v>
       </c>
     </row>
     <row r="213">
@@ -2537,7 +2537,7 @@
         </is>
       </c>
       <c r="B213" t="n">
-        <v>0.01887171877545971</v>
+        <v>0.09317176407457634</v>
       </c>
     </row>
     <row r="214">
@@ -2547,7 +2547,7 @@
         </is>
       </c>
       <c r="B214" t="n">
-        <v>0.05517075033944119</v>
+        <v>0.2270263879809799</v>
       </c>
     </row>
     <row r="215">
@@ -2557,7 +2557,7 @@
         </is>
       </c>
       <c r="B215" t="n">
-        <v>0.06364130558050972</v>
+        <v>0.1730165532713556</v>
       </c>
     </row>
     <row r="216">
@@ -2567,7 +2567,7 @@
         </is>
       </c>
       <c r="B216" t="n">
-        <v>0.1141926245074901</v>
+        <v>0.2795736608931443</v>
       </c>
     </row>
     <row r="217">
@@ -2577,7 +2577,7 @@
         </is>
       </c>
       <c r="B217" t="n">
-        <v>0.1327108210048863</v>
+        <v>0.3157595620911275</v>
       </c>
     </row>
     <row r="218">
@@ -2587,7 +2587,7 @@
         </is>
       </c>
       <c r="B218" t="n">
-        <v>0.1141001481126966</v>
+        <v>0.1204948067900434</v>
       </c>
     </row>
     <row r="219">
@@ -2597,7 +2597,7 @@
         </is>
       </c>
       <c r="B219" t="n">
-        <v>0.1508671687645879</v>
+        <v>0.2695682164418427</v>
       </c>
     </row>
     <row r="220">
@@ -2607,7 +2607,7 @@
         </is>
       </c>
       <c r="B220" t="n">
-        <v>0.05962516560183738</v>
+        <v>0.1671003282873363</v>
       </c>
     </row>
     <row r="221">
@@ -2617,7 +2617,7 @@
         </is>
       </c>
       <c r="B221" t="n">
-        <v>0.1450167102555082</v>
+        <v>0.1640547016521675</v>
       </c>
     </row>
     <row r="222">
@@ -2637,7 +2637,7 @@
         </is>
       </c>
       <c r="B223" t="n">
-        <v>0.1076236378700315</v>
+        <v>0.2167441604644543</v>
       </c>
     </row>
     <row r="224">
@@ -2647,7 +2647,7 @@
         </is>
       </c>
       <c r="B224" t="n">
-        <v>0.0452169999980076</v>
+        <v>0.2437755167342903</v>
       </c>
     </row>
     <row r="225">
@@ -2657,7 +2657,7 @@
         </is>
       </c>
       <c r="B225" t="n">
-        <v>0.04087897631776809</v>
+        <v>0.2146587338334379</v>
       </c>
     </row>
     <row r="226">
@@ -2667,7 +2667,7 @@
         </is>
       </c>
       <c r="B226" t="n">
-        <v>0.08180145140296793</v>
+        <v>0.1993876391113981</v>
       </c>
     </row>
     <row r="227">
@@ -2677,7 +2677,7 @@
         </is>
       </c>
       <c r="B227" t="n">
-        <v>0.1215317611020903</v>
+        <v>0.192675997841435</v>
       </c>
     </row>
     <row r="228">
@@ -2687,7 +2687,7 @@
         </is>
       </c>
       <c r="B228" t="n">
-        <v>0.03067412503764302</v>
+        <v>0.07978636985270791</v>
       </c>
     </row>
     <row r="229">
@@ -2717,7 +2717,7 @@
         </is>
       </c>
       <c r="B231" t="n">
-        <v>0.07251189160085911</v>
+        <v>0.2092499628013908</v>
       </c>
     </row>
     <row r="232">
@@ -2727,7 +2727,7 @@
         </is>
       </c>
       <c r="B232" t="n">
-        <v>0.1620903430782231</v>
+        <v>0.3178963819873079</v>
       </c>
     </row>
     <row r="233">
@@ -2757,7 +2757,7 @@
         </is>
       </c>
       <c r="B235" t="n">
-        <v>0.02402662620204664</v>
+        <v>0.2088373318420442</v>
       </c>
     </row>
     <row r="236">
@@ -2767,7 +2767,7 @@
         </is>
       </c>
       <c r="B236" t="n">
-        <v>0.04059218260013678</v>
+        <v>0.1716615745071335</v>
       </c>
     </row>
     <row r="237">
@@ -2777,7 +2777,7 @@
         </is>
       </c>
       <c r="B237" t="n">
-        <v>0.02082712967373208</v>
+        <v>0.09167856748511079</v>
       </c>
     </row>
     <row r="238">
@@ -2787,7 +2787,7 @@
         </is>
       </c>
       <c r="B238" t="n">
-        <v>0.05718636260608315</v>
+        <v>0.1822484352975021</v>
       </c>
     </row>
     <row r="239">
@@ -2797,7 +2797,7 @@
         </is>
       </c>
       <c r="B239" t="n">
-        <v>0.06067571077053117</v>
+        <v>0.166444864540406</v>
       </c>
     </row>
     <row r="240">
@@ -2807,7 +2807,7 @@
         </is>
       </c>
       <c r="B240" t="n">
-        <v>0.1323586653078712</v>
+        <v>0.2038880662990325</v>
       </c>
     </row>
     <row r="241">
@@ -2817,7 +2817,7 @@
         </is>
       </c>
       <c r="B241" t="n">
-        <v>0.02511515924379994</v>
+        <v>0.08374506221452181</v>
       </c>
     </row>
     <row r="242">
@@ -2827,7 +2827,7 @@
         </is>
       </c>
       <c r="B242" t="n">
-        <v>0.06965900110769273</v>
+        <v>0.1580176494565002</v>
       </c>
     </row>
     <row r="243">
@@ -2837,7 +2837,7 @@
         </is>
       </c>
       <c r="B243" t="n">
-        <v>0.01491855905412042</v>
+        <v>0.1404556871069677</v>
       </c>
     </row>
     <row r="244">
@@ -2857,7 +2857,7 @@
         </is>
       </c>
       <c r="B245" t="n">
-        <v>0.1055605854125545</v>
+        <v>0.1864702639099592</v>
       </c>
     </row>
     <row r="246">
@@ -2867,7 +2867,7 @@
         </is>
       </c>
       <c r="B246" t="n">
-        <v>0.07396031269071095</v>
+        <v>0.1868572601713004</v>
       </c>
     </row>
     <row r="247">
@@ -2877,7 +2877,7 @@
         </is>
       </c>
       <c r="B247" t="n">
-        <v>0.1269977865304976</v>
+        <v>0.2440469380679715</v>
       </c>
     </row>
     <row r="248">
@@ -2887,7 +2887,7 @@
         </is>
       </c>
       <c r="B248" t="n">
-        <v>0.04818598564312843</v>
+        <v>0.1675100400783077</v>
       </c>
     </row>
     <row r="249">
@@ -2897,7 +2897,7 @@
         </is>
       </c>
       <c r="B249" t="n">
-        <v>0.01661070603823309</v>
+        <v>0.049573243595488</v>
       </c>
     </row>
     <row r="250">
@@ -2907,7 +2907,7 @@
         </is>
       </c>
       <c r="B250" t="n">
-        <v>0.1707275334085102</v>
+        <v>0.2859283442156704</v>
       </c>
     </row>
     <row r="251">
@@ -2917,7 +2917,7 @@
         </is>
       </c>
       <c r="B251" t="n">
-        <v>0.02734739503234051</v>
+        <v>0.09479442670945605</v>
       </c>
     </row>
     <row r="252">
@@ -2927,7 +2927,7 @@
         </is>
       </c>
       <c r="B252" t="n">
-        <v>0.2299423601663837</v>
+        <v>0.327887727713414</v>
       </c>
     </row>
     <row r="253">
@@ -2947,7 +2947,7 @@
         </is>
       </c>
       <c r="B254" t="n">
-        <v>0.03398846425668441</v>
+        <v>0.1101472385418248</v>
       </c>
     </row>
     <row r="255">
@@ -2957,7 +2957,7 @@
         </is>
       </c>
       <c r="B255" t="n">
-        <v>0.05880378324293799</v>
+        <v>0.1434799313749668</v>
       </c>
     </row>
     <row r="256">
@@ -2967,7 +2967,7 @@
         </is>
       </c>
       <c r="B256" t="n">
-        <v>0.3270495379840007</v>
+        <v>0.33100784453549</v>
       </c>
     </row>
     <row r="257">
@@ -2977,7 +2977,7 @@
         </is>
       </c>
       <c r="B257" t="n">
-        <v>0.2177013760599194</v>
+        <v>0.2876545193627201</v>
       </c>
     </row>
     <row r="258">
@@ -2987,7 +2987,7 @@
         </is>
       </c>
       <c r="B258" t="n">
-        <v>0.05994474654361059</v>
+        <v>0.1071701812765737</v>
       </c>
     </row>
     <row r="259">
@@ -3007,7 +3007,7 @@
         </is>
       </c>
       <c r="B260" t="n">
-        <v>0.09666202023709809</v>
+        <v>0.1732564377410726</v>
       </c>
     </row>
     <row r="261">
@@ -3017,7 +3017,7 @@
         </is>
       </c>
       <c r="B261" t="n">
-        <v>0.4888132548832806</v>
+        <v>0.4495406400422166</v>
       </c>
     </row>
     <row r="262">
@@ -3027,7 +3027,7 @@
         </is>
       </c>
       <c r="B262" t="n">
-        <v>0.2148907099555648</v>
+        <v>0.2776167963327291</v>
       </c>
     </row>
     <row r="263">
@@ -3045,7 +3045,7 @@
         </is>
       </c>
       <c r="B264" t="n">
-        <v>0.03936924861198607</v>
+        <v>0.1444139274998807</v>
       </c>
     </row>
     <row r="265">
@@ -3055,7 +3055,7 @@
         </is>
       </c>
       <c r="B265" t="n">
-        <v>0.02011293864425934</v>
+        <v>0.04719472242169778</v>
       </c>
     </row>
     <row r="266">
@@ -3083,7 +3083,7 @@
         </is>
       </c>
       <c r="B268" t="n">
-        <v>0.0475213228236847</v>
+        <v>0.07503952951131292</v>
       </c>
     </row>
     <row r="269">
@@ -3093,7 +3093,7 @@
         </is>
       </c>
       <c r="B269" t="n">
-        <v>0.0976702300950348</v>
+        <v>0.1749799487993168</v>
       </c>
     </row>
     <row r="270">
@@ -3103,7 +3103,7 @@
         </is>
       </c>
       <c r="B270" t="n">
-        <v>0.1461645783390761</v>
+        <v>0.2574932232224773</v>
       </c>
     </row>
     <row r="271">
@@ -3113,7 +3113,7 @@
         </is>
       </c>
       <c r="B271" t="n">
-        <v>0.2366798679104326</v>
+        <v>0.222487598846158</v>
       </c>
     </row>
     <row r="272">
@@ -3123,7 +3123,7 @@
         </is>
       </c>
       <c r="B272" t="n">
-        <v>0.05419028945675704</v>
+        <v>0.2483969997286532</v>
       </c>
     </row>
     <row r="273">
@@ -3133,7 +3133,7 @@
         </is>
       </c>
       <c r="B273" t="n">
-        <v>0.03418755029264493</v>
+        <v>0.1613224335266789</v>
       </c>
     </row>
     <row r="274">
@@ -3143,7 +3143,7 @@
         </is>
       </c>
       <c r="B274" t="n">
-        <v>0.03823716935999313</v>
+        <v>0.2673248437210549</v>
       </c>
     </row>
     <row r="275">
@@ -3153,7 +3153,7 @@
         </is>
       </c>
       <c r="B275" t="n">
-        <v>0.1972870837916141</v>
+        <v>0.374847936951972</v>
       </c>
     </row>
     <row r="276">
@@ -3163,7 +3163,7 @@
         </is>
       </c>
       <c r="B276" t="n">
-        <v>0.0447450702431005</v>
+        <v>0.09713522786717237</v>
       </c>
     </row>
     <row r="277">
@@ -3173,7 +3173,7 @@
         </is>
       </c>
       <c r="B277" t="n">
-        <v>0.1469469991462353</v>
+        <v>0.1819500080663995</v>
       </c>
     </row>
     <row r="278">
@@ -3183,7 +3183,7 @@
         </is>
       </c>
       <c r="B278" t="n">
-        <v>0.1459939195174091</v>
+        <v>0.2732407982844711</v>
       </c>
     </row>
     <row r="279">
@@ -3193,7 +3193,7 @@
         </is>
       </c>
       <c r="B279" t="n">
-        <v>0.151163777605671</v>
+        <v>0.3081788236441437</v>
       </c>
     </row>
     <row r="280">
@@ -3203,7 +3203,7 @@
         </is>
       </c>
       <c r="B280" t="n">
-        <v>0.1104439839878246</v>
+        <v>0.1714106090797951</v>
       </c>
     </row>
     <row r="281">
@@ -3223,7 +3223,7 @@
         </is>
       </c>
       <c r="B282" t="n">
-        <v>0.09905977321959183</v>
+        <v>0.3842659889460942</v>
       </c>
     </row>
     <row r="283">
@@ -3243,7 +3243,7 @@
         </is>
       </c>
       <c r="B284" t="n">
-        <v>0.0410574755568072</v>
+        <v>0.09867143169804142</v>
       </c>
     </row>
     <row r="285">
@@ -3253,7 +3253,7 @@
         </is>
       </c>
       <c r="B285" t="n">
-        <v>0.09394508508384819</v>
+        <v>0.3197335531955452</v>
       </c>
     </row>
     <row r="286">
@@ -3283,7 +3283,7 @@
         </is>
       </c>
       <c r="B288" t="n">
-        <v>0.1755240629253653</v>
+        <v>0.2160572932864098</v>
       </c>
     </row>
     <row r="289">
@@ -3293,7 +3293,7 @@
         </is>
       </c>
       <c r="B289" t="n">
-        <v>0.07464648445346225</v>
+        <v>0.1360709646302288</v>
       </c>
     </row>
     <row r="290">
@@ -3303,7 +3303,7 @@
         </is>
       </c>
       <c r="B290" t="n">
-        <v>0.06616878343225559</v>
+        <v>0.238874190868941</v>
       </c>
     </row>
     <row r="291">
@@ -3313,7 +3313,7 @@
         </is>
       </c>
       <c r="B291" t="n">
-        <v>0.08584752131072616</v>
+        <v>0.1789634607628287</v>
       </c>
     </row>
     <row r="292">
@@ -3323,7 +3323,7 @@
         </is>
       </c>
       <c r="B292" t="n">
-        <v>0.06225880601859298</v>
+        <v>0.266586550527505</v>
       </c>
     </row>
     <row r="293">
@@ -3333,7 +3333,7 @@
         </is>
       </c>
       <c r="B293" t="n">
-        <v>0.1934363031582823</v>
+        <v>0.3140730377384913</v>
       </c>
     </row>
     <row r="294">
@@ -3343,7 +3343,7 @@
         </is>
       </c>
       <c r="B294" t="n">
-        <v>0.08558569597854711</v>
+        <v>0.2502745873205987</v>
       </c>
     </row>
     <row r="295">
@@ -3353,7 +3353,7 @@
         </is>
       </c>
       <c r="B295" t="n">
-        <v>0.01567946842493163</v>
+        <v>0.02388289569521925</v>
       </c>
     </row>
     <row r="296">
@@ -3363,7 +3363,7 @@
         </is>
       </c>
       <c r="B296" t="n">
-        <v>0.06616391938374445</v>
+        <v>0.1834930348580958</v>
       </c>
     </row>
     <row r="297">
@@ -3373,7 +3373,7 @@
         </is>
       </c>
       <c r="B297" t="n">
-        <v>0.06952301736453317</v>
+        <v>0.1209942066798312</v>
       </c>
     </row>
     <row r="298">
@@ -3383,7 +3383,7 @@
         </is>
       </c>
       <c r="B298" t="n">
-        <v>0.06553612645991126</v>
+        <v>0.1456884875087667</v>
       </c>
     </row>
     <row r="299">
@@ -3393,7 +3393,7 @@
         </is>
       </c>
       <c r="B299" t="n">
-        <v>0.1040452889143821</v>
+        <v>0.1906040394074381</v>
       </c>
     </row>
     <row r="300">
@@ -3403,7 +3403,7 @@
         </is>
       </c>
       <c r="B300" t="n">
-        <v>0.1503111038007348</v>
+        <v>0.2958101406838924</v>
       </c>
     </row>
     <row r="301">
@@ -3413,7 +3413,7 @@
         </is>
       </c>
       <c r="B301" t="n">
-        <v>0.07583087666550956</v>
+        <v>0.2814248568587029</v>
       </c>
     </row>
     <row r="302">
@@ -3423,7 +3423,7 @@
         </is>
       </c>
       <c r="B302" t="n">
-        <v>0.0649571588581484</v>
+        <v>0.1627066767666151</v>
       </c>
     </row>
     <row r="303">
@@ -3433,7 +3433,7 @@
         </is>
       </c>
       <c r="B303" t="n">
-        <v>0.03512700996305018</v>
+        <v>0.1540644700753639</v>
       </c>
     </row>
     <row r="304">
@@ -3453,7 +3453,7 @@
         </is>
       </c>
       <c r="B305" t="n">
-        <v>0.2990633290874951</v>
+        <v>0.3210232183396567</v>
       </c>
     </row>
     <row r="306">
@@ -3463,7 +3463,7 @@
         </is>
       </c>
       <c r="B306" t="n">
-        <v>0.1226961726802403</v>
+        <v>0.2854437762414585</v>
       </c>
     </row>
     <row r="307">
@@ -3493,7 +3493,7 @@
         </is>
       </c>
       <c r="B309" t="n">
-        <v>0.1661295303416647</v>
+        <v>0.2912781040854209</v>
       </c>
     </row>
     <row r="310">
@@ -3503,7 +3503,7 @@
         </is>
       </c>
       <c r="B310" t="n">
-        <v>0.07960664382462621</v>
+        <v>0.123083374297843</v>
       </c>
     </row>
     <row r="311">
@@ -3523,7 +3523,7 @@
         </is>
       </c>
       <c r="B312" t="n">
-        <v>0.01492032726946774</v>
+        <v>0.06228366421500865</v>
       </c>
     </row>
     <row r="313">
@@ -3553,7 +3553,7 @@
         </is>
       </c>
       <c r="B315" t="n">
-        <v>0.06780574227431783</v>
+        <v>0.09786649867540639</v>
       </c>
     </row>
     <row r="316">
@@ -3563,7 +3563,7 @@
         </is>
       </c>
       <c r="B316" t="n">
-        <v>0.1043834295664304</v>
+        <v>0.1781896811833408</v>
       </c>
     </row>
     <row r="317">
@@ -3573,7 +3573,7 @@
         </is>
       </c>
       <c r="B317" t="n">
-        <v>0.07822777547086589</v>
+        <v>0.1601730738984948</v>
       </c>
     </row>
     <row r="318">
@@ -3593,7 +3593,7 @@
         </is>
       </c>
       <c r="B319" t="n">
-        <v>0.06913362510807607</v>
+        <v>0.2339568624884023</v>
       </c>
     </row>
     <row r="320">
@@ -3603,7 +3603,7 @@
         </is>
       </c>
       <c r="B320" t="n">
-        <v>0.0270531522423967</v>
+        <v>0.06012382568299117</v>
       </c>
     </row>
     <row r="321">
@@ -3613,7 +3613,7 @@
         </is>
       </c>
       <c r="B321" t="n">
-        <v>0.07730774109598718</v>
+        <v>0.1307425780970204</v>
       </c>
     </row>
     <row r="322">
@@ -3623,7 +3623,7 @@
         </is>
       </c>
       <c r="B322" t="n">
-        <v>0.1545241588104194</v>
+        <v>0.2351701342313084</v>
       </c>
     </row>
     <row r="323">
@@ -3633,7 +3633,7 @@
         </is>
       </c>
       <c r="B323" t="n">
-        <v>0.01862828207118615</v>
+        <v>0.05674286802376202</v>
       </c>
     </row>
     <row r="324">
@@ -3643,7 +3643,7 @@
         </is>
       </c>
       <c r="B324" t="n">
-        <v>0.1371475168900045</v>
+        <v>0.2457863003446607</v>
       </c>
     </row>
     <row r="325">
@@ -3653,7 +3653,7 @@
         </is>
       </c>
       <c r="B325" t="n">
-        <v>0.2150037306560495</v>
+        <v>0.2904935569336328</v>
       </c>
     </row>
     <row r="326">
@@ -3663,7 +3663,7 @@
         </is>
       </c>
       <c r="B326" t="n">
-        <v>0.09866934985393373</v>
+        <v>0.3571666814363856</v>
       </c>
     </row>
     <row r="327">
@@ -3673,7 +3673,7 @@
         </is>
       </c>
       <c r="B327" t="n">
-        <v>0.2136303297743392</v>
+        <v>0.3161447717918626</v>
       </c>
     </row>
     <row r="328">
@@ -3683,7 +3683,7 @@
         </is>
       </c>
       <c r="B328" t="n">
-        <v>0.2473067417845193</v>
+        <v>0.3241116409144129</v>
       </c>
     </row>
     <row r="329">
@@ -3693,7 +3693,7 @@
         </is>
       </c>
       <c r="B329" t="n">
-        <v>0.08608265140683401</v>
+        <v>0.2652237412722075</v>
       </c>
     </row>
     <row r="330">
@@ -3703,7 +3703,7 @@
         </is>
       </c>
       <c r="B330" t="n">
-        <v>0.0792590214569226</v>
+        <v>0.1695412014665872</v>
       </c>
     </row>
     <row r="331">
@@ -3713,7 +3713,7 @@
         </is>
       </c>
       <c r="B331" t="n">
-        <v>0.09091847095125563</v>
+        <v>0.1668489728680489</v>
       </c>
     </row>
     <row r="332">
@@ -3723,7 +3723,7 @@
         </is>
       </c>
       <c r="B332" t="n">
-        <v>0.03957060391620788</v>
+        <v>0.116309820704704</v>
       </c>
     </row>
     <row r="333">
@@ -3763,7 +3763,7 @@
         </is>
       </c>
       <c r="B336" t="n">
-        <v>0.2866546602957682</v>
+        <v>0.3019572878115548</v>
       </c>
     </row>
     <row r="337">
@@ -3773,7 +3773,7 @@
         </is>
       </c>
       <c r="B337" t="n">
-        <v>0.08507457959973511</v>
+        <v>0.2055675637859565</v>
       </c>
     </row>
     <row r="338">
@@ -3783,7 +3783,7 @@
         </is>
       </c>
       <c r="B338" t="n">
-        <v>0.08446813833447582</v>
+        <v>0.1472638176005927</v>
       </c>
     </row>
     <row r="339">
@@ -3793,7 +3793,7 @@
         </is>
       </c>
       <c r="B339" t="n">
-        <v>0.1965516646378216</v>
+        <v>0.2259445301681852</v>
       </c>
     </row>
     <row r="340">
@@ -3803,7 +3803,7 @@
         </is>
       </c>
       <c r="B340" t="n">
-        <v>0.06805506014529107</v>
+        <v>0.1949828680838322</v>
       </c>
     </row>
     <row r="341">
@@ -3823,7 +3823,7 @@
         </is>
       </c>
       <c r="B342" t="n">
-        <v>0.04290506054838621</v>
+        <v>0.1234550628859094</v>
       </c>
     </row>
     <row r="343">
@@ -3833,7 +3833,7 @@
         </is>
       </c>
       <c r="B343" t="n">
-        <v>0.09805289352675817</v>
+        <v>0.2070638775750116</v>
       </c>
     </row>
     <row r="344">
@@ -3843,7 +3843,7 @@
         </is>
       </c>
       <c r="B344" t="n">
-        <v>0.2435800954780838</v>
+        <v>0.3229751770217689</v>
       </c>
     </row>
     <row r="345">
@@ -3861,7 +3861,7 @@
         </is>
       </c>
       <c r="B346" t="n">
-        <v>0.1663171932563019</v>
+        <v>0.278890389844238</v>
       </c>
     </row>
     <row r="347">
@@ -3871,7 +3871,7 @@
         </is>
       </c>
       <c r="B347" t="n">
-        <v>0.09556187904434678</v>
+        <v>0.2242583072545949</v>
       </c>
     </row>
     <row r="348">
@@ -3891,7 +3891,7 @@
         </is>
       </c>
       <c r="B349" t="n">
-        <v>0.1739191204551745</v>
+        <v>0.3515538609923212</v>
       </c>
     </row>
     <row r="350">
@@ -3901,7 +3901,7 @@
         </is>
       </c>
       <c r="B350" t="n">
-        <v>0.02046915434001889</v>
+        <v>0.2899350358146964</v>
       </c>
     </row>
     <row r="351">
@@ -3921,7 +3921,7 @@
         </is>
       </c>
       <c r="B352" t="n">
-        <v>0.01294496436148429</v>
+        <v>0.1894065732006348</v>
       </c>
     </row>
     <row r="353">
@@ -3951,7 +3951,7 @@
         </is>
       </c>
       <c r="B355" t="n">
-        <v>0.03172144260277259</v>
+        <v>0.08147295980859658</v>
       </c>
     </row>
     <row r="356">
@@ -3961,7 +3961,7 @@
         </is>
       </c>
       <c r="B356" t="n">
-        <v>0.03537655530075686</v>
+        <v>0.1616473446721606</v>
       </c>
     </row>
     <row r="357">
@@ -3971,7 +3971,7 @@
         </is>
       </c>
       <c r="B357" t="n">
-        <v>0.05223316704283627</v>
+        <v>0.09172328540163321</v>
       </c>
     </row>
     <row r="358">
@@ -3981,7 +3981,7 @@
         </is>
       </c>
       <c r="B358" t="n">
-        <v>0.1228824418013327</v>
+        <v>0.3215169064460345</v>
       </c>
     </row>
     <row r="359">
@@ -3991,7 +3991,7 @@
         </is>
       </c>
       <c r="B359" t="n">
-        <v>0.06521116170694875</v>
+        <v>0.1277053475789979</v>
       </c>
     </row>
     <row r="360">
@@ -4011,7 +4011,7 @@
         </is>
       </c>
       <c r="B361" t="n">
-        <v>0.1762512797222832</v>
+        <v>0.2128505657666913</v>
       </c>
     </row>
     <row r="362">
@@ -4021,7 +4021,7 @@
         </is>
       </c>
       <c r="B362" t="n">
-        <v>0.04533553054574907</v>
+        <v>0.0961221837552179</v>
       </c>
     </row>
     <row r="363">
@@ -4031,7 +4031,7 @@
         </is>
       </c>
       <c r="B363" t="n">
-        <v>0.1056922474305686</v>
+        <v>0.2869721921773026</v>
       </c>
     </row>
     <row r="364">
@@ -4041,7 +4041,7 @@
         </is>
       </c>
       <c r="B364" t="n">
-        <v>0.1592959709067024</v>
+        <v>0.3501432713675214</v>
       </c>
     </row>
     <row r="365">
@@ -4051,7 +4051,7 @@
         </is>
       </c>
       <c r="B365" t="n">
-        <v>0.07163915218158796</v>
+        <v>0.182630359089844</v>
       </c>
     </row>
     <row r="366">
@@ -4061,7 +4061,7 @@
         </is>
       </c>
       <c r="B366" t="n">
-        <v>0.1300194933561499</v>
+        <v>0.1751815760560006</v>
       </c>
     </row>
     <row r="367">
@@ -4079,7 +4079,7 @@
         </is>
       </c>
       <c r="B368" t="n">
-        <v>0.01893311009307609</v>
+        <v>0.1119372120255259</v>
       </c>
     </row>
     <row r="369">
@@ -4089,7 +4089,7 @@
         </is>
       </c>
       <c r="B369" t="n">
-        <v>0.08829523544790528</v>
+        <v>0.2007447613042364</v>
       </c>
     </row>
     <row r="370">
@@ -4099,7 +4099,7 @@
         </is>
       </c>
       <c r="B370" t="n">
-        <v>0.0675977341348783</v>
+        <v>0.1523496456199335</v>
       </c>
     </row>
     <row r="371">
@@ -4109,7 +4109,7 @@
         </is>
       </c>
       <c r="B371" t="n">
-        <v>0.06098368072906391</v>
+        <v>0.2042237937929176</v>
       </c>
     </row>
     <row r="372">
@@ -4119,7 +4119,7 @@
         </is>
       </c>
       <c r="B372" t="n">
-        <v>0.1134183684750844</v>
+        <v>0.2266995044871047</v>
       </c>
     </row>
     <row r="373">
@@ -4129,7 +4129,7 @@
         </is>
       </c>
       <c r="B373" t="n">
-        <v>0.05859333488521323</v>
+        <v>0.09961006144430427</v>
       </c>
     </row>
     <row r="374">
@@ -4139,7 +4139,7 @@
         </is>
       </c>
       <c r="B374" t="n">
-        <v>0.01830448615101303</v>
+        <v>0.1220548455999478</v>
       </c>
     </row>
     <row r="375">
@@ -4149,7 +4149,7 @@
         </is>
       </c>
       <c r="B375" t="n">
-        <v>0.1582325626656656</v>
+        <v>0.2162050015029229</v>
       </c>
     </row>
     <row r="376">
@@ -4159,7 +4159,7 @@
         </is>
       </c>
       <c r="B376" t="n">
-        <v>0.1569160803800217</v>
+        <v>0.196494421783085</v>
       </c>
     </row>
     <row r="377">
@@ -4169,7 +4169,7 @@
         </is>
       </c>
       <c r="B377" t="n">
-        <v>0.1408213214063785</v>
+        <v>0.2989604814992112</v>
       </c>
     </row>
     <row r="378">
@@ -4179,7 +4179,7 @@
         </is>
       </c>
       <c r="B378" t="n">
-        <v>0.01099875876231123</v>
+        <v>0.02304693640233276</v>
       </c>
     </row>
     <row r="379">
@@ -4189,7 +4189,7 @@
         </is>
       </c>
       <c r="B379" t="n">
-        <v>0.06177545979661851</v>
+        <v>0.1623406887318471</v>
       </c>
     </row>
     <row r="380">
@@ -4199,7 +4199,7 @@
         </is>
       </c>
       <c r="B380" t="n">
-        <v>0.03931879119818674</v>
+        <v>0.1575762692205978</v>
       </c>
     </row>
     <row r="381">
@@ -4209,7 +4209,7 @@
         </is>
       </c>
       <c r="B381" t="n">
-        <v>0.1781301131071457</v>
+        <v>0.2451740035103852</v>
       </c>
     </row>
     <row r="382">
@@ -4219,7 +4219,7 @@
         </is>
       </c>
       <c r="B382" t="n">
-        <v>0.02991571363939376</v>
+        <v>0.1332118741549194</v>
       </c>
     </row>
     <row r="383">
@@ -4229,7 +4229,7 @@
         </is>
       </c>
       <c r="B383" t="n">
-        <v>0.1746487541407533</v>
+        <v>0.2139844393632162</v>
       </c>
     </row>
     <row r="384">
@@ -4239,7 +4239,7 @@
         </is>
       </c>
       <c r="B384" t="n">
-        <v>0.1360246189915116</v>
+        <v>0.2193477552553307</v>
       </c>
     </row>
     <row r="385">
@@ -4259,7 +4259,7 @@
         </is>
       </c>
       <c r="B386" t="n">
-        <v>0.1273009787812747</v>
+        <v>0.2957682756366525</v>
       </c>
     </row>
     <row r="387">
@@ -4269,7 +4269,7 @@
         </is>
       </c>
       <c r="B387" t="n">
-        <v>0.08395889329301909</v>
+        <v>0.1625518414357363</v>
       </c>
     </row>
     <row r="388">
@@ -4289,7 +4289,7 @@
         </is>
       </c>
       <c r="B389" t="n">
-        <v>0.07033438020374846</v>
+        <v>0.165351916817029</v>
       </c>
     </row>
     <row r="390">
@@ -4299,7 +4299,7 @@
         </is>
       </c>
       <c r="B390" t="n">
-        <v>0.1587482328428312</v>
+        <v>0.2465251387997798</v>
       </c>
     </row>
     <row r="391">
@@ -4309,7 +4309,7 @@
         </is>
       </c>
       <c r="B391" t="n">
-        <v>0.1827005286322304</v>
+        <v>0.2741662255756874</v>
       </c>
     </row>
     <row r="392">
@@ -4319,7 +4319,7 @@
         </is>
       </c>
       <c r="B392" t="n">
-        <v>0.09461392893365582</v>
+        <v>0.1867011484011805</v>
       </c>
     </row>
     <row r="393">
@@ -4329,7 +4329,7 @@
         </is>
       </c>
       <c r="B393" t="n">
-        <v>0.09488106990674892</v>
+        <v>0.1808166234503759</v>
       </c>
     </row>
     <row r="394">
@@ -4347,7 +4347,7 @@
         </is>
       </c>
       <c r="B395" t="n">
-        <v>0.0535432130958911</v>
+        <v>0.09157054468320552</v>
       </c>
     </row>
     <row r="396">
@@ -4357,7 +4357,7 @@
         </is>
       </c>
       <c r="B396" t="n">
-        <v>0.1671392147468322</v>
+        <v>0.2869921534659147</v>
       </c>
     </row>
     <row r="397">
@@ -4367,7 +4367,7 @@
         </is>
       </c>
       <c r="B397" t="n">
-        <v>0.1103065714190774</v>
+        <v>0.2267002966026932</v>
       </c>
     </row>
     <row r="398">
@@ -4387,7 +4387,7 @@
         </is>
       </c>
       <c r="B399" t="n">
-        <v>0.07370956491839836</v>
+        <v>0.2313090927634855</v>
       </c>
     </row>
     <row r="400">
@@ -4407,7 +4407,7 @@
         </is>
       </c>
       <c r="B401" t="n">
-        <v>0.1676696518013656</v>
+        <v>0.2359381132363977</v>
       </c>
     </row>
     <row r="402">
@@ -4447,7 +4447,7 @@
         </is>
       </c>
       <c r="B405" t="n">
-        <v>0.03953923625819539</v>
+        <v>0.1347194048618512</v>
       </c>
     </row>
     <row r="406">
@@ -4457,7 +4457,7 @@
         </is>
       </c>
       <c r="B406" t="n">
-        <v>0.1405332437547643</v>
+        <v>0.2414688386039076</v>
       </c>
     </row>
     <row r="407">
@@ -4467,7 +4467,7 @@
         </is>
       </c>
       <c r="B407" t="n">
-        <v>0.06759782432985376</v>
+        <v>0.2136795039156257</v>
       </c>
     </row>
     <row r="408">
@@ -4477,7 +4477,7 @@
         </is>
       </c>
       <c r="B408" t="n">
-        <v>0.08443116681487739</v>
+        <v>0.2438226092855627</v>
       </c>
     </row>
     <row r="409">
@@ -4487,7 +4487,7 @@
         </is>
       </c>
       <c r="B409" t="n">
-        <v>0.3063588243293557</v>
+        <v>0.3400261380834546</v>
       </c>
     </row>
     <row r="410">
@@ -4497,7 +4497,7 @@
         </is>
       </c>
       <c r="B410" t="n">
-        <v>0.06609999862094176</v>
+        <v>0.1582902619958874</v>
       </c>
     </row>
     <row r="411">
@@ -4507,7 +4507,7 @@
         </is>
       </c>
       <c r="B411" t="n">
-        <v>0.0600302220307776</v>
+        <v>0.1054251753129305</v>
       </c>
     </row>
     <row r="412">
@@ -4517,7 +4517,7 @@
         </is>
       </c>
       <c r="B412" t="n">
-        <v>0.0586950116533708</v>
+        <v>0.1216293956390025</v>
       </c>
     </row>
     <row r="413">
@@ -4537,7 +4537,7 @@
         </is>
       </c>
       <c r="B414" t="n">
-        <v>0.2661173914757911</v>
+        <v>0.2171426152584958</v>
       </c>
     </row>
     <row r="415">
@@ -4547,7 +4547,7 @@
         </is>
       </c>
       <c r="B415" t="n">
-        <v>0.03093772997853415</v>
+        <v>0.09730103614507786</v>
       </c>
     </row>
     <row r="416">
@@ -4557,7 +4557,7 @@
         </is>
       </c>
       <c r="B416" t="n">
-        <v>0.1171943097042696</v>
+        <v>0.3869478329305405</v>
       </c>
     </row>
     <row r="417">
@@ -4567,7 +4567,7 @@
         </is>
       </c>
       <c r="B417" t="n">
-        <v>0</v>
+        <v>0.246125015049887</v>
       </c>
     </row>
     <row r="418">
@@ -4577,7 +4577,7 @@
         </is>
       </c>
       <c r="B418" t="n">
-        <v>0.2307559570081736</v>
+        <v>0.2589901383543265</v>
       </c>
     </row>
     <row r="419">
@@ -4587,7 +4587,7 @@
         </is>
       </c>
       <c r="B419" t="n">
-        <v>0.2251833792882407</v>
+        <v>0.3105728362086421</v>
       </c>
     </row>
     <row r="420">
@@ -4597,7 +4597,7 @@
         </is>
       </c>
       <c r="B420" t="n">
-        <v>0.1336251663619753</v>
+        <v>0.1943313446024788</v>
       </c>
     </row>
     <row r="421">
@@ -4627,7 +4627,7 @@
         </is>
       </c>
       <c r="B423" t="n">
-        <v>0.05876321812159222</v>
+        <v>0.1369577194350778</v>
       </c>
     </row>
     <row r="424">
@@ -4637,7 +4637,7 @@
         </is>
       </c>
       <c r="B424" t="n">
-        <v>0.04304566956911923</v>
+        <v>0.1088877556862159</v>
       </c>
     </row>
     <row r="425">
@@ -4647,7 +4647,7 @@
         </is>
       </c>
       <c r="B425" t="n">
-        <v>0.2652369696482713</v>
+        <v>0.2254943904168004</v>
       </c>
     </row>
     <row r="426">
@@ -4657,7 +4657,7 @@
         </is>
       </c>
       <c r="B426" t="n">
-        <v>0.1308616333985118</v>
+        <v>0.1835223078223814</v>
       </c>
     </row>
     <row r="427">
@@ -4667,7 +4667,7 @@
         </is>
       </c>
       <c r="B427" t="n">
-        <v>0.01618355449813067</v>
+        <v>0.09083769477277577</v>
       </c>
     </row>
     <row r="428">
@@ -4677,7 +4677,7 @@
         </is>
       </c>
       <c r="B428" t="n">
-        <v>0.008103947669436486</v>
+        <v>0.1481773349833964</v>
       </c>
     </row>
     <row r="429">
@@ -4697,7 +4697,7 @@
         </is>
       </c>
       <c r="B430" t="n">
-        <v>0.03749084515344817</v>
+        <v>0.1797012887698027</v>
       </c>
     </row>
     <row r="431">
@@ -4707,7 +4707,7 @@
         </is>
       </c>
       <c r="B431" t="n">
-        <v>0.07482408108114751</v>
+        <v>0.1762452588300779</v>
       </c>
     </row>
     <row r="432">
@@ -4717,7 +4717,7 @@
         </is>
       </c>
       <c r="B432" t="n">
-        <v>0.07687590316479478</v>
+        <v>0.2144223887058835</v>
       </c>
     </row>
     <row r="433">
@@ -4727,7 +4727,7 @@
         </is>
       </c>
       <c r="B433" t="n">
-        <v>0.02780528013635072</v>
+        <v>0.1229826087657539</v>
       </c>
     </row>
     <row r="434">
@@ -4737,7 +4737,7 @@
         </is>
       </c>
       <c r="B434" t="n">
-        <v>0.1104847917385279</v>
+        <v>0.1422467841270336</v>
       </c>
     </row>
     <row r="435">
@@ -4747,7 +4747,7 @@
         </is>
       </c>
       <c r="B435" t="n">
-        <v>0.0154460310837434</v>
+        <v>0.05549440803880593</v>
       </c>
     </row>
     <row r="436">
@@ -4767,7 +4767,7 @@
         </is>
       </c>
       <c r="B437" t="n">
-        <v>0.04832076560814991</v>
+        <v>0.1333223259739143</v>
       </c>
     </row>
     <row r="438">
@@ -4777,7 +4777,7 @@
         </is>
       </c>
       <c r="B438" t="n">
-        <v>0.2142550577925915</v>
+        <v>0.2791721378393806</v>
       </c>
     </row>
     <row r="439">
@@ -4787,7 +4787,7 @@
         </is>
       </c>
       <c r="B439" t="n">
-        <v>0.02768346960993453</v>
+        <v>0.1009817998339175</v>
       </c>
     </row>
     <row r="440">
@@ -4797,7 +4797,7 @@
         </is>
       </c>
       <c r="B440" t="n">
-        <v>0.1978212920745512</v>
+        <v>0.2096243258865428</v>
       </c>
     </row>
     <row r="441">
@@ -4817,7 +4817,7 @@
         </is>
       </c>
       <c r="B442" t="n">
-        <v>0.07961765739203328</v>
+        <v>0.0771925012947688</v>
       </c>
     </row>
     <row r="443">
@@ -4827,7 +4827,7 @@
         </is>
       </c>
       <c r="B443" t="n">
-        <v>0.09110161555122698</v>
+        <v>0.1283316958408963</v>
       </c>
     </row>
     <row r="444">
@@ -4837,7 +4837,7 @@
         </is>
       </c>
       <c r="B444" t="n">
-        <v>0.1577448805739654</v>
+        <v>0.2716804642836509</v>
       </c>
     </row>
     <row r="445">
@@ -4847,7 +4847,7 @@
         </is>
       </c>
       <c r="B445" t="n">
-        <v>0.09232232806826418</v>
+        <v>0.1978202778610796</v>
       </c>
     </row>
     <row r="446">
@@ -4857,7 +4857,7 @@
         </is>
       </c>
       <c r="B446" t="n">
-        <v>0.03905909992528339</v>
+        <v>0.1493661504007931</v>
       </c>
     </row>
     <row r="447">
@@ -4867,7 +4867,7 @@
         </is>
       </c>
       <c r="B447" t="n">
-        <v>0.1509392066849256</v>
+        <v>0.1662949572187789</v>
       </c>
     </row>
     <row r="448">
@@ -4877,7 +4877,7 @@
         </is>
       </c>
       <c r="B448" t="n">
-        <v>0.09120122695824114</v>
+        <v>0.2507479528226679</v>
       </c>
     </row>
     <row r="449">
@@ -4897,7 +4897,7 @@
         </is>
       </c>
       <c r="B450" t="n">
-        <v>0.01332895237892416</v>
+        <v>0.03734298644842202</v>
       </c>
     </row>
     <row r="451">
@@ -4917,7 +4917,7 @@
         </is>
       </c>
       <c r="B452" t="n">
-        <v>0.1034261045050385</v>
+        <v>0.1578056268907661</v>
       </c>
     </row>
     <row r="453">
@@ -4927,7 +4927,7 @@
         </is>
       </c>
       <c r="B453" t="n">
-        <v>0.03959483358244819</v>
+        <v>0.09128780913330553</v>
       </c>
     </row>
     <row r="454">
@@ -4945,7 +4945,7 @@
         </is>
       </c>
       <c r="B455" t="n">
-        <v>0.1340620333565985</v>
+        <v>0.2626978428850406</v>
       </c>
     </row>
     <row r="456">
@@ -4955,7 +4955,7 @@
         </is>
       </c>
       <c r="B456" t="n">
-        <v>0.03744601397670317</v>
+        <v>0.1150198415741327</v>
       </c>
     </row>
     <row r="457">
@@ -4965,7 +4965,7 @@
         </is>
       </c>
       <c r="B457" t="n">
-        <v>0.09019114347179003</v>
+        <v>0.2116303105623551</v>
       </c>
     </row>
     <row r="458">
@@ -4975,7 +4975,7 @@
         </is>
       </c>
       <c r="B458" t="n">
-        <v>0.04478212676317846</v>
+        <v>0.117499371779139</v>
       </c>
     </row>
     <row r="459">
@@ -4985,7 +4985,7 @@
         </is>
       </c>
       <c r="B459" t="n">
-        <v>0.1189233466391697</v>
+        <v>0.2125131842204771</v>
       </c>
     </row>
     <row r="460">
@@ -4995,7 +4995,7 @@
         </is>
       </c>
       <c r="B460" t="n">
-        <v>0.1916045048730479</v>
+        <v>0.2119385052149479</v>
       </c>
     </row>
     <row r="461">
@@ -5005,7 +5005,7 @@
         </is>
       </c>
       <c r="B461" t="n">
-        <v>0.1155322401993424</v>
+        <v>0.2191788074809272</v>
       </c>
     </row>
     <row r="462">
@@ -5015,7 +5015,7 @@
         </is>
       </c>
       <c r="B462" t="n">
-        <v>0.1002173963456282</v>
+        <v>0.07701689211923245</v>
       </c>
     </row>
     <row r="463">
@@ -5025,7 +5025,7 @@
         </is>
       </c>
       <c r="B463" t="n">
-        <v>0.08627717291349171</v>
+        <v>0.2519229991931081</v>
       </c>
     </row>
     <row r="464">
@@ -5035,7 +5035,7 @@
         </is>
       </c>
       <c r="B464" t="n">
-        <v>0.1315365421640229</v>
+        <v>0.2091507069670976</v>
       </c>
     </row>
     <row r="465">
@@ -5045,7 +5045,7 @@
         </is>
       </c>
       <c r="B465" t="n">
-        <v>0.07460681773004486</v>
+        <v>0.1827860899297528</v>
       </c>
     </row>
     <row r="466">
@@ -5085,7 +5085,7 @@
         </is>
       </c>
       <c r="B469" t="n">
-        <v>0.1134020426996102</v>
+        <v>0.2921066932186132</v>
       </c>
     </row>
     <row r="470">
@@ -5105,7 +5105,7 @@
         </is>
       </c>
       <c r="B471" t="n">
-        <v>0.1952105693703184</v>
+        <v>0.3210460750542804</v>
       </c>
     </row>
     <row r="472">
@@ -5115,7 +5115,7 @@
         </is>
       </c>
       <c r="B472" t="n">
-        <v>0.0699178192186023</v>
+        <v>0.2326138173589417</v>
       </c>
     </row>
     <row r="473">
@@ -5125,7 +5125,7 @@
         </is>
       </c>
       <c r="B473" t="n">
-        <v>0.0790775083285709</v>
+        <v>0.09587991895087138</v>
       </c>
     </row>
     <row r="474">
@@ -5135,7 +5135,7 @@
         </is>
       </c>
       <c r="B474" t="n">
-        <v>0.291134966428945</v>
+        <v>0.4716871738650495</v>
       </c>
     </row>
     <row r="475">
@@ -5145,7 +5145,7 @@
         </is>
       </c>
       <c r="B475" t="n">
-        <v>0.08421606452113223</v>
+        <v>0.08355239596172316</v>
       </c>
     </row>
     <row r="476">
@@ -5155,7 +5155,7 @@
         </is>
       </c>
       <c r="B476" t="n">
-        <v>0.1620360382207147</v>
+        <v>0.2410794618786731</v>
       </c>
     </row>
     <row r="477">
@@ -5165,7 +5165,7 @@
         </is>
       </c>
       <c r="B477" t="n">
-        <v>0.204039887407361</v>
+        <v>0.2886036027833009</v>
       </c>
     </row>
     <row r="478">
@@ -5185,7 +5185,7 @@
         </is>
       </c>
       <c r="B479" t="n">
-        <v>0.2332699524907672</v>
+        <v>0.2849098445607743</v>
       </c>
     </row>
     <row r="480">
@@ -5195,7 +5195,7 @@
         </is>
       </c>
       <c r="B480" t="n">
-        <v>0.1194018113212649</v>
+        <v>0.2507915570226495</v>
       </c>
     </row>
     <row r="481">
@@ -5205,7 +5205,7 @@
         </is>
       </c>
       <c r="B481" t="n">
-        <v>0.1404797474049164</v>
+        <v>0.1992768528832978</v>
       </c>
     </row>
     <row r="482">
@@ -5235,7 +5235,7 @@
         </is>
       </c>
       <c r="B484" t="n">
-        <v>0.04867634566657204</v>
+        <v>0.1448488271531087</v>
       </c>
     </row>
     <row r="485">
@@ -5245,7 +5245,7 @@
         </is>
       </c>
       <c r="B485" t="n">
-        <v>0.1443853521959526</v>
+        <v>0.2712151383196789</v>
       </c>
     </row>
   </sheetData>
